--- a/research/traditional_assets/database/data/denmark/denmark_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_retail_special_lines.xlsx
@@ -1145,7 +1145,7 @@
         <v>5.21324245374878</v>
       </c>
       <c r="H2">
-        <v>1.22015579357352</v>
+        <v>1.22015579357351</v>
       </c>
       <c r="I2">
         <v>0.427260394222329</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08811073712690345</v>
+        <v>0.08795199350522427</v>
       </c>
       <c r="C2">
-        <v>1069.302874692152</v>
+        <v>1060.74122986792</v>
       </c>
       <c r="D2">
-        <v>1054.002874692152</v>
+        <v>1057.97222986792</v>
       </c>
       <c r="E2">
-        <v>-535.4</v>
+        <v>-522.869</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.531</v>
       </c>
       <c r="G2">
         <v>15.3</v>
@@ -1457,28 +1457,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6303093</v>
       </c>
       <c r="N2">
-        <v>33.27500000000001</v>
+        <v>32.64469070000001</v>
       </c>
       <c r="O2">
-        <v>7.320500000000001</v>
+        <v>7.181831954000002</v>
       </c>
       <c r="P2">
-        <v>25.9545</v>
+        <v>25.462858746</v>
       </c>
       <c r="Q2">
-        <v>121.0545</v>
+        <v>120.562858746</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08811073712690345</v>
+        <v>0.08844409444972148</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765235</v>
+        <v>0.9848520658134294</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>52.79154218413088</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08795199350522427</v>
+        <v>0.08779324988354507</v>
       </c>
       <c r="C3">
-        <v>1060.74122986792</v>
+        <v>1052.209595096165</v>
       </c>
       <c r="D3">
-        <v>1057.97222986792</v>
+        <v>1061.971595096164</v>
       </c>
       <c r="E3">
-        <v>-522.869</v>
+        <v>-510.338</v>
       </c>
       <c r="F3">
-        <v>12.531</v>
+        <v>25.062</v>
       </c>
       <c r="G3">
         <v>15.3</v>
@@ -1539,28 +1539,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M3">
-        <v>0.6303093</v>
+        <v>1.2606186</v>
       </c>
       <c r="N3">
-        <v>32.64469070000001</v>
+        <v>32.0143814</v>
       </c>
       <c r="O3">
-        <v>7.181831954000002</v>
+        <v>7.043163908000001</v>
       </c>
       <c r="P3">
-        <v>25.462858746</v>
+        <v>24.971217492</v>
       </c>
       <c r="Q3">
-        <v>120.562858746</v>
+        <v>120.071217492</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08844409444972148</v>
+        <v>0.08878425498320927</v>
       </c>
       <c r="T3">
-        <v>0.9848520658134294</v>
+        <v>0.99270796727966</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>52.79154218413088</v>
+        <v>26.39577109206544</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08779324988354507</v>
+        <v>0.08763450626186589</v>
       </c>
       <c r="C4">
-        <v>1052.209595096165</v>
+        <v>1043.708312001887</v>
       </c>
       <c r="D4">
-        <v>1061.971595096164</v>
+        <v>1066.001312001887</v>
       </c>
       <c r="E4">
-        <v>-510.338</v>
+        <v>-497.807</v>
       </c>
       <c r="F4">
-        <v>25.062</v>
+        <v>37.593</v>
       </c>
       <c r="G4">
         <v>15.3</v>
@@ -1621,28 +1621,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M4">
-        <v>1.2606186</v>
+        <v>1.8909279</v>
       </c>
       <c r="N4">
-        <v>32.0143814</v>
+        <v>31.3840721</v>
       </c>
       <c r="O4">
-        <v>7.043163908000001</v>
+        <v>6.904495862000001</v>
       </c>
       <c r="P4">
-        <v>24.971217492</v>
+        <v>24.479576238</v>
       </c>
       <c r="Q4">
-        <v>120.071217492</v>
+        <v>119.579576238</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08878425498320927</v>
+        <v>0.08913142913594423</v>
       </c>
       <c r="T4">
-        <v>0.99270796727966</v>
+        <v>1.00072584609571</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.39577109206544</v>
+        <v>17.59718072804363</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08763450626186589</v>
+        <v>0.08747576264018671</v>
       </c>
       <c r="C5">
-        <v>1043.708312001887</v>
+        <v>1035.237727415107</v>
       </c>
       <c r="D5">
-        <v>1066.001312001887</v>
+        <v>1070.061727415107</v>
       </c>
       <c r="E5">
-        <v>-497.807</v>
+        <v>-485.276</v>
       </c>
       <c r="F5">
-        <v>37.593</v>
+        <v>50.124</v>
       </c>
       <c r="G5">
         <v>15.3</v>
@@ -1703,28 +1703,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M5">
-        <v>1.8909279</v>
+        <v>2.5212372</v>
       </c>
       <c r="N5">
-        <v>31.3840721</v>
+        <v>30.7537628</v>
       </c>
       <c r="O5">
-        <v>6.904495862000001</v>
+        <v>6.765827816000001</v>
       </c>
       <c r="P5">
-        <v>24.479576238</v>
+        <v>23.987934984</v>
       </c>
       <c r="Q5">
-        <v>119.579576238</v>
+        <v>119.087934984</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08913142913594423</v>
+        <v>0.08948583608352782</v>
       </c>
       <c r="T5">
-        <v>1.00072584609571</v>
+        <v>1.00891076405376</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.59718072804363</v>
+        <v>13.19788554603272</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08747576264018671</v>
+        <v>0.08737551901850753</v>
       </c>
       <c r="C6">
-        <v>1035.237727415107</v>
+        <v>1025.286776095405</v>
       </c>
       <c r="D6">
-        <v>1070.061727415107</v>
+        <v>1072.641776095405</v>
       </c>
       <c r="E6">
-        <v>-485.276</v>
+        <v>-472.745</v>
       </c>
       <c r="F6">
-        <v>50.124</v>
+        <v>62.655</v>
       </c>
       <c r="G6">
         <v>15.3</v>
@@ -1785,45 +1785,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M6">
-        <v>2.5212372</v>
+        <v>3.245529</v>
       </c>
       <c r="N6">
-        <v>30.7537628</v>
+        <v>30.029471</v>
       </c>
       <c r="O6">
-        <v>6.765827816000001</v>
+        <v>6.606483620000001</v>
       </c>
       <c r="P6">
-        <v>23.987934984</v>
+        <v>23.42298738</v>
       </c>
       <c r="Q6">
-        <v>119.087934984</v>
+        <v>118.52298738</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08948583608352782</v>
+        <v>0.08984770423000793</v>
       </c>
       <c r="T6">
-        <v>1.00891076405376</v>
+        <v>1.017267996074086</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.19788554603272</v>
+        <v>10.25256591452426</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08737551901850753</v>
+        <v>0.08730803539682833</v>
       </c>
       <c r="C7">
-        <v>1025.286776095405</v>
+        <v>1014.499673418496</v>
       </c>
       <c r="D7">
-        <v>1072.641776095405</v>
+        <v>1074.385673418496</v>
       </c>
       <c r="E7">
-        <v>-472.745</v>
+        <v>-460.2139999999999</v>
       </c>
       <c r="F7">
-        <v>62.655</v>
+        <v>75.18600000000001</v>
       </c>
       <c r="G7">
         <v>15.3</v>
@@ -1867,45 +1867,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M7">
-        <v>3.245529</v>
+        <v>4.022451</v>
       </c>
       <c r="N7">
-        <v>30.029471</v>
+        <v>29.25254900000001</v>
       </c>
       <c r="O7">
-        <v>6.606483620000001</v>
+        <v>6.435560780000001</v>
       </c>
       <c r="P7">
-        <v>23.42298738</v>
+        <v>22.81698822000001</v>
       </c>
       <c r="Q7">
-        <v>118.52298738</v>
+        <v>117.91698822</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08984770423000793</v>
+        <v>0.09021727169875354</v>
       </c>
       <c r="T7">
-        <v>1.017267996074086</v>
+        <v>1.025803041541653</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.25256591452426</v>
+        <v>8.272319538510228</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08730803539682833</v>
+        <v>0.08721793177514915</v>
       </c>
       <c r="C8">
-        <v>1014.499673418496</v>
+        <v>1004.305971204894</v>
       </c>
       <c r="D8">
-        <v>1074.385673418496</v>
+        <v>1076.722971204894</v>
       </c>
       <c r="E8">
-        <v>-460.214</v>
+        <v>-447.683</v>
       </c>
       <c r="F8">
-        <v>75.18599999999999</v>
+        <v>87.71699999999998</v>
       </c>
       <c r="G8">
         <v>15.3</v>
@@ -1949,45 +1949,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M8">
-        <v>4.022450999999999</v>
+        <v>4.763033099999999</v>
       </c>
       <c r="N8">
-        <v>29.25254900000001</v>
+        <v>28.5119669</v>
       </c>
       <c r="O8">
-        <v>6.435560780000001</v>
+        <v>6.272632718000001</v>
       </c>
       <c r="P8">
-        <v>22.81698822000001</v>
+        <v>22.239334182</v>
       </c>
       <c r="Q8">
-        <v>117.91698822</v>
+        <v>117.339334182</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09021727169875354</v>
+        <v>0.09059478685499908</v>
       </c>
       <c r="T8">
-        <v>1.025803041541653</v>
+        <v>1.034521636374113</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.27231953851023</v>
+        <v>6.986094637889459</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08721793177514915</v>
+        <v>0.08709038815346996</v>
       </c>
       <c r="C9">
-        <v>1004.305971204894</v>
+        <v>995.1009062089977</v>
       </c>
       <c r="D9">
-        <v>1076.722971204894</v>
+        <v>1080.048906208998</v>
       </c>
       <c r="E9">
-        <v>-447.683</v>
+        <v>-435.152</v>
       </c>
       <c r="F9">
-        <v>87.717</v>
+        <v>100.248</v>
       </c>
       <c r="G9">
         <v>15.3</v>
@@ -2031,28 +2031,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M9">
-        <v>4.7630331</v>
+        <v>5.443466399999999</v>
       </c>
       <c r="N9">
-        <v>28.5119669</v>
+        <v>27.83153360000001</v>
       </c>
       <c r="O9">
-        <v>6.272632718000001</v>
+        <v>6.122937392000002</v>
       </c>
       <c r="P9">
-        <v>22.239334182</v>
+        <v>21.70859620800001</v>
       </c>
       <c r="Q9">
-        <v>117.339334182</v>
+        <v>116.808596208</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0905947868549991</v>
+        <v>0.09098050886246735</v>
       </c>
       <c r="T9">
-        <v>1.034521636374113</v>
+        <v>1.043429765876844</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>6.986094637889458</v>
+        <v>6.112832808153278</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08709038815346996</v>
+        <v>0.0870330445317908</v>
       </c>
       <c r="C10">
-        <v>995.1009062089977</v>
+        <v>984.0719518759117</v>
       </c>
       <c r="D10">
-        <v>1080.048906208998</v>
+        <v>1081.550951875912</v>
       </c>
       <c r="E10">
-        <v>-435.152</v>
+        <v>-422.621</v>
       </c>
       <c r="F10">
-        <v>100.248</v>
+        <v>112.779</v>
       </c>
       <c r="G10">
         <v>15.3</v>
@@ -2113,45 +2113,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M10">
-        <v>5.443466399999999</v>
+        <v>6.236678699999999</v>
       </c>
       <c r="N10">
-        <v>27.83153360000001</v>
+        <v>27.03832130000001</v>
       </c>
       <c r="O10">
-        <v>6.122937392000002</v>
+        <v>5.948430686000002</v>
       </c>
       <c r="P10">
-        <v>21.70859620800001</v>
+        <v>21.08989061400001</v>
       </c>
       <c r="Q10">
-        <v>116.808596208</v>
+        <v>116.189890614</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09098050886246735</v>
+        <v>0.09137470827669317</v>
       </c>
       <c r="T10">
-        <v>1.043429765876844</v>
+        <v>1.05253367844557</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.112832808153278</v>
+        <v>5.335371854253132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0870330445317908</v>
+        <v>0.0869133009101116</v>
       </c>
       <c r="C11">
-        <v>984.0719518759117</v>
+        <v>974.6909988227953</v>
       </c>
       <c r="D11">
-        <v>1081.550951875912</v>
+        <v>1084.700998822795</v>
       </c>
       <c r="E11">
-        <v>-422.621</v>
+        <v>-410.09</v>
       </c>
       <c r="F11">
-        <v>112.779</v>
+        <v>125.31</v>
       </c>
       <c r="G11">
         <v>15.3</v>
@@ -2195,28 +2195,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M11">
-        <v>6.236678699999999</v>
+        <v>6.929642999999999</v>
       </c>
       <c r="N11">
-        <v>27.03832130000001</v>
+        <v>26.34535700000001</v>
       </c>
       <c r="O11">
-        <v>5.948430686000002</v>
+        <v>5.795978540000002</v>
       </c>
       <c r="P11">
-        <v>21.08989061400001</v>
+        <v>20.54937846000001</v>
       </c>
       <c r="Q11">
-        <v>116.189890614</v>
+        <v>115.64937846</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09137470827669317</v>
+        <v>0.09177766767790177</v>
       </c>
       <c r="T11">
-        <v>1.05253367844557</v>
+        <v>1.061839900182489</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.335371854253132</v>
+        <v>4.801834668827819</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0869133009101116</v>
+        <v>0.08700805728843242</v>
       </c>
       <c r="C12">
-        <v>974.6909988227953</v>
+        <v>959.6657696605222</v>
       </c>
       <c r="D12">
-        <v>1084.700998822795</v>
+        <v>1082.206769660522</v>
       </c>
       <c r="E12">
-        <v>-410.09</v>
+        <v>-397.559</v>
       </c>
       <c r="F12">
-        <v>125.31</v>
+        <v>137.841</v>
       </c>
       <c r="G12">
         <v>15.3</v>
@@ -2277,45 +2277,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M12">
-        <v>6.929643</v>
+        <v>7.967209799999999</v>
       </c>
       <c r="N12">
-        <v>26.34535700000001</v>
+        <v>25.30779020000001</v>
       </c>
       <c r="O12">
-        <v>5.795978540000002</v>
+        <v>5.567713844000002</v>
       </c>
       <c r="P12">
-        <v>20.54937846000001</v>
+        <v>19.740076356</v>
       </c>
       <c r="Q12">
-        <v>115.64937846</v>
+        <v>114.840076356</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09177766767790177</v>
+        <v>0.09218968234655327</v>
       </c>
       <c r="T12">
-        <v>1.061839900182489</v>
+        <v>1.071355250497766</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.801834668827818</v>
+        <v>4.176493507174872</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08700805728843242</v>
+        <v>0.08723541366675321</v>
       </c>
       <c r="C13">
-        <v>959.6657696605222</v>
+        <v>941.1966942325058</v>
       </c>
       <c r="D13">
-        <v>1082.206769660522</v>
+        <v>1076.268694232506</v>
       </c>
       <c r="E13">
-        <v>-397.559</v>
+        <v>-385.028</v>
       </c>
       <c r="F13">
-        <v>137.841</v>
+        <v>150.372</v>
       </c>
       <c r="G13">
         <v>15.3</v>
@@ -2359,45 +2359,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M13">
-        <v>7.967209799999999</v>
+        <v>9.2178036</v>
       </c>
       <c r="N13">
-        <v>25.30779020000001</v>
+        <v>24.05719640000001</v>
       </c>
       <c r="O13">
-        <v>5.567713844000002</v>
+        <v>5.292583208000002</v>
       </c>
       <c r="P13">
-        <v>19.740076356</v>
+        <v>18.76461319200001</v>
       </c>
       <c r="Q13">
-        <v>114.840076356</v>
+        <v>113.864613192</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09218968234655327</v>
+        <v>0.09261106098494683</v>
       </c>
       <c r="T13">
-        <v>1.071355250497766</v>
+        <v>1.081086858774754</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.176493507174872</v>
+        <v>3.609862115092147</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08723541366675321</v>
+        <v>0.08744639004507403</v>
       </c>
       <c r="C14">
-        <v>941.1966942325058</v>
+        <v>923.2134264377819</v>
       </c>
       <c r="D14">
-        <v>1076.268694232506</v>
+        <v>1070.816426437782</v>
       </c>
       <c r="E14">
-        <v>-385.028</v>
+        <v>-372.497</v>
       </c>
       <c r="F14">
-        <v>150.372</v>
+        <v>162.903</v>
       </c>
       <c r="G14">
         <v>15.3</v>
@@ -2441,45 +2441,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M14">
-        <v>9.2178036</v>
+        <v>10.4420823</v>
       </c>
       <c r="N14">
-        <v>24.05719640000001</v>
+        <v>22.8329177</v>
       </c>
       <c r="O14">
-        <v>5.292583208000002</v>
+        <v>5.023241894000001</v>
       </c>
       <c r="P14">
-        <v>18.76461319200001</v>
+        <v>17.809675806</v>
       </c>
       <c r="Q14">
-        <v>113.864613192</v>
+        <v>112.909675806</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09261106098494683</v>
+        <v>0.09304212648859084</v>
       </c>
       <c r="T14">
-        <v>1.081086858774754</v>
+        <v>1.091042182184546</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.609862115092147</v>
+        <v>3.186624951232189</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08744639004507403</v>
+        <v>0.08824704642339484</v>
       </c>
       <c r="C15">
-        <v>923.2134264377819</v>
+        <v>890.4841777001366</v>
       </c>
       <c r="D15">
-        <v>1070.816426437782</v>
+        <v>1050.618177700137</v>
       </c>
       <c r="E15">
-        <v>-372.497</v>
+        <v>-359.966</v>
       </c>
       <c r="F15">
-        <v>162.903</v>
+        <v>175.434</v>
       </c>
       <c r="G15">
         <v>15.3</v>
@@ -2523,45 +2523,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M15">
-        <v>10.4420823</v>
+        <v>12.6137046</v>
       </c>
       <c r="N15">
-        <v>22.8329177</v>
+        <v>20.66129540000001</v>
       </c>
       <c r="O15">
-        <v>5.023241894000001</v>
+        <v>4.545484988000002</v>
       </c>
       <c r="P15">
-        <v>17.809675806</v>
+        <v>16.11581041200001</v>
       </c>
       <c r="Q15">
-        <v>112.909675806</v>
+        <v>111.215810412</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09304212648859084</v>
+        <v>0.09348321677138935</v>
       </c>
       <c r="T15">
-        <v>1.091042182184546</v>
+        <v>1.101229024743403</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.186624951232189</v>
+        <v>2.63800374713072</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08824704642339484</v>
+        <v>0.08871308280171565</v>
       </c>
       <c r="C16">
-        <v>890.4841777001366</v>
+        <v>866.5434569677494</v>
       </c>
       <c r="D16">
-        <v>1050.618177700137</v>
+        <v>1039.208456967749</v>
       </c>
       <c r="E16">
-        <v>-359.966</v>
+        <v>-347.4349999999999</v>
       </c>
       <c r="F16">
-        <v>175.434</v>
+        <v>187.965</v>
       </c>
       <c r="G16">
         <v>15.3</v>
@@ -2605,45 +2605,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M16">
-        <v>12.6137046</v>
+        <v>14.247747</v>
       </c>
       <c r="N16">
-        <v>20.66129540000001</v>
+        <v>19.027253</v>
       </c>
       <c r="O16">
-        <v>4.545484988000002</v>
+        <v>4.185995660000001</v>
       </c>
       <c r="P16">
-        <v>16.11581041200001</v>
+        <v>14.84125734</v>
       </c>
       <c r="Q16">
-        <v>111.215810412</v>
+        <v>109.94125734</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09348321677138935</v>
+        <v>0.09393468564907723</v>
       </c>
       <c r="T16">
-        <v>1.101229024743403</v>
+        <v>1.11165555771541</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.63800374713072</v>
+        <v>2.33545696733666</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08871308280171565</v>
+        <v>0.08875323918003646</v>
       </c>
       <c r="C17">
-        <v>866.5434569677495</v>
+        <v>853.0409156183936</v>
       </c>
       <c r="D17">
-        <v>1039.208456967749</v>
+        <v>1038.236915618394</v>
       </c>
       <c r="E17">
-        <v>-347.435</v>
+        <v>-334.904</v>
       </c>
       <c r="F17">
-        <v>187.965</v>
+        <v>200.496</v>
       </c>
       <c r="G17">
         <v>15.3</v>
@@ -2687,28 +2687,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M17">
-        <v>14.247747</v>
+        <v>15.1975968</v>
       </c>
       <c r="N17">
-        <v>19.02725300000001</v>
+        <v>18.07740320000001</v>
       </c>
       <c r="O17">
-        <v>4.185995660000002</v>
+        <v>3.977028704000001</v>
       </c>
       <c r="P17">
-        <v>14.84125734000001</v>
+        <v>14.100374496</v>
       </c>
       <c r="Q17">
-        <v>109.94125734</v>
+        <v>109.200374496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09393468564907723</v>
+        <v>0.09439690378575769</v>
       </c>
       <c r="T17">
-        <v>1.11165555771541</v>
+        <v>1.122330341472464</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.335456967336661</v>
+        <v>2.189490906878119</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08875323918003646</v>
+        <v>0.08879339555835727</v>
       </c>
       <c r="C18">
-        <v>853.0409156183936</v>
+        <v>839.5401891329939</v>
       </c>
       <c r="D18">
-        <v>1038.236915618394</v>
+        <v>1037.267189132994</v>
       </c>
       <c r="E18">
-        <v>-334.904</v>
+        <v>-322.373</v>
       </c>
       <c r="F18">
-        <v>200.496</v>
+        <v>213.027</v>
       </c>
       <c r="G18">
         <v>15.3</v>
@@ -2769,28 +2769,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M18">
-        <v>15.1975968</v>
+        <v>16.1474466</v>
       </c>
       <c r="N18">
-        <v>18.07740320000001</v>
+        <v>17.1275534</v>
       </c>
       <c r="O18">
-        <v>3.977028704000001</v>
+        <v>3.768061748000001</v>
       </c>
       <c r="P18">
-        <v>14.100374496</v>
+        <v>13.359491652</v>
       </c>
       <c r="Q18">
-        <v>109.200374496</v>
+        <v>108.459491652</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09439690378575769</v>
+        <v>0.09487025970886419</v>
       </c>
       <c r="T18">
-        <v>1.122330341472464</v>
+        <v>1.133262348934508</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.189490906878119</v>
+        <v>2.060697324120583</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08879339555835727</v>
+        <v>0.09082723193667808</v>
       </c>
       <c r="C19">
-        <v>839.5401891329939</v>
+        <v>780.1568366218727</v>
       </c>
       <c r="D19">
-        <v>1037.267189132994</v>
+        <v>990.4148366218727</v>
       </c>
       <c r="E19">
-        <v>-322.373</v>
+        <v>-309.842</v>
       </c>
       <c r="F19">
-        <v>213.027</v>
+        <v>225.558</v>
       </c>
       <c r="G19">
         <v>15.3</v>
@@ -2851,45 +2851,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M19">
-        <v>16.1474466</v>
+        <v>20.30022</v>
       </c>
       <c r="N19">
-        <v>17.1275534</v>
+        <v>12.97478000000001</v>
       </c>
       <c r="O19">
-        <v>3.768061748000001</v>
+        <v>2.854451600000001</v>
       </c>
       <c r="P19">
-        <v>13.359491652</v>
+        <v>10.12032840000001</v>
       </c>
       <c r="Q19">
-        <v>108.459491652</v>
+        <v>105.2203284</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09487025970886419</v>
+        <v>0.09535516089838791</v>
       </c>
       <c r="T19">
-        <v>1.133262348934508</v>
+        <v>1.144460990724894</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.060697324120583</v>
+        <v>1.639144797445545</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09082723193667809</v>
+        <v>0.09097814831499891</v>
       </c>
       <c r="C20">
-        <v>780.1568366218725</v>
+        <v>764.3173827397873</v>
       </c>
       <c r="D20">
-        <v>990.4148366218725</v>
+        <v>987.1063827397873</v>
       </c>
       <c r="E20">
-        <v>-309.842</v>
+        <v>-297.311</v>
       </c>
       <c r="F20">
-        <v>225.558</v>
+        <v>238.089</v>
       </c>
       <c r="G20">
         <v>15.3</v>
@@ -2933,28 +2933,28 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M20">
-        <v>20.30022</v>
+        <v>21.42801</v>
       </c>
       <c r="N20">
-        <v>12.97478000000001</v>
+        <v>11.84699000000001</v>
       </c>
       <c r="O20">
-        <v>2.854451600000002</v>
+        <v>2.606337800000001</v>
       </c>
       <c r="P20">
-        <v>10.12032840000001</v>
+        <v>9.240652200000003</v>
       </c>
       <c r="Q20">
-        <v>105.2203284</v>
+        <v>104.3406522</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09535516089838791</v>
+        <v>0.09585203495678876</v>
       </c>
       <c r="T20">
-        <v>1.144460990724894</v>
+        <v>1.155936142189117</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.639144797445546</v>
+        <v>1.552874018632622</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09097814831499891</v>
+        <v>0.1007850675387763</v>
       </c>
       <c r="C21">
-        <v>764.3173827397873</v>
+        <v>575.7299915390786</v>
       </c>
       <c r="D21">
-        <v>987.1063827397873</v>
+        <v>811.0499915390786</v>
       </c>
       <c r="E21">
-        <v>-297.311</v>
+        <v>-284.78</v>
       </c>
       <c r="F21">
-        <v>238.089</v>
+        <v>250.62</v>
       </c>
       <c r="G21">
         <v>15.3</v>
@@ -3015,45 +3015,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M21">
-        <v>21.42801</v>
+        <v>36.79101600000001</v>
       </c>
       <c r="N21">
-        <v>11.84699000000001</v>
+        <v>-3.516016</v>
       </c>
       <c r="O21">
-        <v>2.606337800000001</v>
+        <v>-0.7735235200000001</v>
       </c>
       <c r="P21">
-        <v>9.240652200000003</v>
+        <v>-2.74249248</v>
       </c>
       <c r="Q21">
-        <v>104.3406522</v>
+        <v>92.35750752</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09585203495678876</v>
+        <v>0.09658372449609029</v>
       </c>
       <c r="T21">
-        <v>1.155936142189117</v>
+        <v>1.172834283974372</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.22</v>
+        <v>0.1989752063384169</v>
       </c>
       <c r="W21">
-        <v>0.0702</v>
+        <v>0.1175904397095204</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.552874018632622</v>
+        <v>0.9044327560837135</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1007850675387763</v>
+        <v>0.1017950675387763</v>
       </c>
       <c r="C22">
-        <v>575.7299915390786</v>
+        <v>548.5698370892298</v>
       </c>
       <c r="D22">
-        <v>811.0499915390786</v>
+        <v>796.4208370892298</v>
       </c>
       <c r="E22">
-        <v>-284.78</v>
+        <v>-272.249</v>
       </c>
       <c r="F22">
-        <v>250.62</v>
+        <v>263.151</v>
       </c>
       <c r="G22">
         <v>15.3</v>
@@ -3097,37 +3097,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M22">
-        <v>36.79101600000001</v>
+        <v>38.6305668</v>
       </c>
       <c r="N22">
-        <v>-3.516016</v>
+        <v>-5.355566799999998</v>
       </c>
       <c r="O22">
-        <v>-0.7735235200000001</v>
+        <v>-1.178224696</v>
       </c>
       <c r="P22">
-        <v>-2.74249248</v>
+        <v>-4.177342103999999</v>
       </c>
       <c r="Q22">
-        <v>92.35750752</v>
+        <v>90.92265789599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09658372449609029</v>
+        <v>0.097226556451737</v>
       </c>
       <c r="T22">
-        <v>1.172834283974372</v>
+        <v>1.187680287568984</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.1989752063384169</v>
+        <v>0.1895001965127781</v>
       </c>
       <c r="W22">
-        <v>0.1175904397095204</v>
+        <v>0.1189813711519242</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9044327560837135</v>
+        <v>0.8613645296035367</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1017950675387763</v>
+        <v>0.1028050675387763</v>
       </c>
       <c r="C23">
-        <v>548.5698370892298</v>
+        <v>521.92807325384</v>
       </c>
       <c r="D23">
-        <v>796.4208370892298</v>
+        <v>782.3100732538401</v>
       </c>
       <c r="E23">
-        <v>-272.249</v>
+        <v>-259.718</v>
       </c>
       <c r="F23">
-        <v>263.151</v>
+        <v>275.682</v>
       </c>
       <c r="G23">
         <v>15.3</v>
@@ -3179,37 +3179,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M23">
-        <v>38.6305668</v>
+        <v>40.47011759999999</v>
       </c>
       <c r="N23">
-        <v>-5.355566799999991</v>
+        <v>-7.195117599999989</v>
       </c>
       <c r="O23">
-        <v>-1.178224695999998</v>
+        <v>-1.582925871999998</v>
       </c>
       <c r="P23">
-        <v>-4.177342103999993</v>
+        <v>-5.612191727999991</v>
       </c>
       <c r="Q23">
-        <v>90.922657896</v>
+        <v>89.48780827200001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.097226556451737</v>
+        <v>0.09788587127804133</v>
       </c>
       <c r="T23">
-        <v>1.187680287568984</v>
+        <v>1.202906957922433</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.1895001965127781</v>
+        <v>0.1808865512167427</v>
       </c>
       <c r="W23">
-        <v>0.1189813711519242</v>
+        <v>0.1202458542813822</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8613645296035368</v>
+        <v>0.8222115964397398</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1028050675387763</v>
+        <v>0.1166878708586054</v>
       </c>
       <c r="C24">
-        <v>521.92807325384</v>
+        <v>356.1881145059172</v>
       </c>
       <c r="D24">
-        <v>782.3100732538401</v>
+        <v>629.1011145059172</v>
       </c>
       <c r="E24">
-        <v>-259.718</v>
+        <v>-247.187</v>
       </c>
       <c r="F24">
-        <v>275.682</v>
+        <v>288.213</v>
       </c>
       <c r="G24">
         <v>15.3</v>
@@ -3261,45 +3261,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M24">
-        <v>40.47011759999999</v>
+        <v>57.87317039999999</v>
       </c>
       <c r="N24">
-        <v>-7.195117599999989</v>
+        <v>-24.59817039999999</v>
       </c>
       <c r="O24">
-        <v>-1.582925871999998</v>
+        <v>-5.411597487999997</v>
       </c>
       <c r="P24">
-        <v>-5.612191727999991</v>
+        <v>-19.18657291199999</v>
       </c>
       <c r="Q24">
-        <v>89.48780827200001</v>
+        <v>75.91342708800001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09788587127804133</v>
+        <v>0.09915036742428746</v>
       </c>
       <c r="T24">
-        <v>1.202906957922433</v>
+        <v>1.23211010217754</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1808865512167427</v>
+        <v>0.1264921197405146</v>
       </c>
       <c r="W24">
-        <v>0.1202458542813822</v>
+        <v>0.1754003823561047</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8222115964397398</v>
+        <v>0.5749641806387025</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1166878708586054</v>
+        <v>0.1182378708586054</v>
       </c>
       <c r="C25">
-        <v>356.1881145059172</v>
+        <v>330.1958308441217</v>
       </c>
       <c r="D25">
-        <v>629.1011145059172</v>
+        <v>615.6398308441218</v>
       </c>
       <c r="E25">
-        <v>-247.187</v>
+        <v>-234.6559999999999</v>
       </c>
       <c r="F25">
-        <v>288.213</v>
+        <v>300.744</v>
       </c>
       <c r="G25">
         <v>15.3</v>
@@ -3343,37 +3343,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M25">
-        <v>57.87317039999999</v>
+        <v>60.38939520000001</v>
       </c>
       <c r="N25">
-        <v>-24.59817039999999</v>
+        <v>-27.1143952</v>
       </c>
       <c r="O25">
-        <v>-5.411597487999997</v>
+        <v>-5.965166944000001</v>
       </c>
       <c r="P25">
-        <v>-19.18657291199999</v>
+        <v>-21.149228256</v>
       </c>
       <c r="Q25">
-        <v>75.91342708800001</v>
+        <v>73.95077174399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09915036742428746</v>
+        <v>0.0998523459430281</v>
       </c>
       <c r="T25">
-        <v>1.23211010217754</v>
+        <v>1.248322077206192</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1264921197405146</v>
+        <v>0.1212216147513264</v>
       </c>
       <c r="W25">
-        <v>0.1754003823561047</v>
+        <v>0.1764586997579337</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5749641806387025</v>
+        <v>0.5510073397787564</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1182378708586054</v>
+        <v>0.1197878708586054</v>
       </c>
       <c r="C26">
-        <v>330.1958308441218</v>
+        <v>304.767558267756</v>
       </c>
       <c r="D26">
-        <v>615.6398308441218</v>
+        <v>602.7425582677561</v>
       </c>
       <c r="E26">
-        <v>-234.656</v>
+        <v>-222.125</v>
       </c>
       <c r="F26">
-        <v>300.744</v>
+        <v>313.275</v>
       </c>
       <c r="G26">
         <v>15.3</v>
@@ -3425,37 +3425,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M26">
-        <v>60.3893952</v>
+        <v>62.90562</v>
       </c>
       <c r="N26">
-        <v>-27.11439519999999</v>
+        <v>-29.63061999999999</v>
       </c>
       <c r="O26">
-        <v>-5.965166943999998</v>
+        <v>-6.518736399999999</v>
       </c>
       <c r="P26">
-        <v>-21.14922825599999</v>
+        <v>-23.1118836</v>
       </c>
       <c r="Q26">
-        <v>73.95077174400001</v>
+        <v>71.9881164</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0998523459430281</v>
+        <v>0.1005730438889351</v>
       </c>
       <c r="T26">
-        <v>1.248322077206192</v>
+        <v>1.264966371568941</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1212216147513264</v>
+        <v>0.1163727501612734</v>
       </c>
       <c r="W26">
-        <v>0.1764586997579337</v>
+        <v>0.1774323517676163</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5510073397787565</v>
+        <v>0.5289670461876061</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1197878708586054</v>
+        <v>0.1213378708586054</v>
       </c>
       <c r="C27">
-        <v>304.767558267756</v>
+        <v>279.8685770856575</v>
       </c>
       <c r="D27">
-        <v>602.7425582677561</v>
+        <v>590.3745770856575</v>
       </c>
       <c r="E27">
-        <v>-222.125</v>
+        <v>-209.594</v>
       </c>
       <c r="F27">
-        <v>313.275</v>
+        <v>325.806</v>
       </c>
       <c r="G27">
         <v>15.3</v>
@@ -3507,37 +3507,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M27">
-        <v>62.90562</v>
+        <v>65.4218448</v>
       </c>
       <c r="N27">
-        <v>-29.63061999999999</v>
+        <v>-32.1468448</v>
       </c>
       <c r="O27">
-        <v>-6.518736399999999</v>
+        <v>-7.072305855999999</v>
       </c>
       <c r="P27">
-        <v>-23.1118836</v>
+        <v>-25.074538944</v>
       </c>
       <c r="Q27">
-        <v>71.9881164</v>
+        <v>70.025461056</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1005730438889351</v>
+        <v>0.1013132201577045</v>
       </c>
       <c r="T27">
-        <v>1.264966371568941</v>
+        <v>1.282060511725278</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1163727501612734</v>
+        <v>0.1118968751550705</v>
       </c>
       <c r="W27">
-        <v>0.1774323517676163</v>
+        <v>0.1783311074688619</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5289670461876061</v>
+        <v>0.5086221597957752</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1213378708586054</v>
+        <v>0.1325205824674141</v>
       </c>
       <c r="C28">
-        <v>279.8685770856575</v>
+        <v>191.2081456533672</v>
       </c>
       <c r="D28">
-        <v>590.3745770856575</v>
+        <v>514.2451456533672</v>
       </c>
       <c r="E28">
-        <v>-209.594</v>
+        <v>-197.063</v>
       </c>
       <c r="F28">
-        <v>325.806</v>
+        <v>338.337</v>
       </c>
       <c r="G28">
         <v>15.3</v>
@@ -3589,45 +3589,45 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M28">
-        <v>65.4218448</v>
+        <v>79.7798646</v>
       </c>
       <c r="N28">
-        <v>-32.1468448</v>
+        <v>-46.50486459999999</v>
       </c>
       <c r="O28">
-        <v>-7.072305855999999</v>
+        <v>-10.231070212</v>
       </c>
       <c r="P28">
-        <v>-25.074538944</v>
+        <v>-36.27379438799999</v>
       </c>
       <c r="Q28">
-        <v>70.025461056</v>
+        <v>58.826205612</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1013132201577045</v>
+        <v>0.1023239651034383</v>
       </c>
       <c r="T28">
-        <v>1.282060511725278</v>
+        <v>1.305403351118668</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1118968751550705</v>
+        <v>0.09175874184173537</v>
       </c>
       <c r="W28">
-        <v>0.1783311074688619</v>
+        <v>0.2141632886737188</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5086221597957752</v>
+        <v>0.4170851901897061</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1325205824674141</v>
+        <v>0.1344205824674141</v>
       </c>
       <c r="C29">
-        <v>191.2081456533672</v>
+        <v>167.6518764716771</v>
       </c>
       <c r="D29">
-        <v>514.2451456533672</v>
+        <v>503.2198764716771</v>
       </c>
       <c r="E29">
-        <v>-197.063</v>
+        <v>-184.532</v>
       </c>
       <c r="F29">
-        <v>338.337</v>
+        <v>350.868</v>
       </c>
       <c r="G29">
         <v>15.3</v>
@@ -3671,37 +3671,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M29">
-        <v>79.7798646</v>
+        <v>82.7346744</v>
       </c>
       <c r="N29">
-        <v>-46.50486459999999</v>
+        <v>-49.4596744</v>
       </c>
       <c r="O29">
-        <v>-10.231070212</v>
+        <v>-10.881128368</v>
       </c>
       <c r="P29">
-        <v>-36.27379438799999</v>
+        <v>-38.578546032</v>
       </c>
       <c r="Q29">
-        <v>58.826205612</v>
+        <v>56.521453968</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1023239651034383</v>
+        <v>0.1031090201743194</v>
       </c>
       <c r="T29">
-        <v>1.305403351118668</v>
+        <v>1.323533953217539</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09175874184173537</v>
+        <v>0.08848164391881623</v>
       </c>
       <c r="W29">
-        <v>0.2141632886737188</v>
+        <v>0.2149360283639432</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4170851901897061</v>
+        <v>0.4021892905400738</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1344205824674141</v>
+        <v>0.1363205824674141</v>
       </c>
       <c r="C30">
-        <v>167.6518764716771</v>
+        <v>144.5584415067854</v>
       </c>
       <c r="D30">
-        <v>503.2198764716771</v>
+        <v>492.6574415067853</v>
       </c>
       <c r="E30">
-        <v>-184.532</v>
+        <v>-172.001</v>
       </c>
       <c r="F30">
-        <v>350.868</v>
+        <v>363.399</v>
       </c>
       <c r="G30">
         <v>15.3</v>
@@ -3753,37 +3753,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M30">
-        <v>82.7346744</v>
+        <v>85.68948420000001</v>
       </c>
       <c r="N30">
-        <v>-49.4596744</v>
+        <v>-52.4144842</v>
       </c>
       <c r="O30">
-        <v>-10.881128368</v>
+        <v>-11.531186524</v>
       </c>
       <c r="P30">
-        <v>-38.578546032</v>
+        <v>-40.88329767600001</v>
       </c>
       <c r="Q30">
-        <v>56.521453968</v>
+        <v>54.21670232399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1031090201743194</v>
+        <v>0.1039161894725493</v>
       </c>
       <c r="T30">
-        <v>1.323533953217539</v>
+        <v>1.342175276502293</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.08848164391881623</v>
+        <v>0.08543055274920187</v>
       </c>
       <c r="W30">
-        <v>0.2149360283639432</v>
+        <v>0.2156554756617382</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4021892905400738</v>
+        <v>0.388320694314554</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.136320582467414</v>
+        <v>0.138220582467414</v>
       </c>
       <c r="C31">
-        <v>144.5584415067855</v>
+        <v>121.8992956558014</v>
       </c>
       <c r="D31">
-        <v>492.6574415067855</v>
+        <v>482.5292956558013</v>
       </c>
       <c r="E31">
-        <v>-172.001</v>
+        <v>-159.47</v>
       </c>
       <c r="F31">
-        <v>363.3989999999999</v>
+        <v>375.9299999999999</v>
       </c>
       <c r="G31">
         <v>15.3</v>
@@ -3835,37 +3835,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M31">
-        <v>85.6894842</v>
+        <v>88.64429399999999</v>
       </c>
       <c r="N31">
-        <v>-52.41448419999999</v>
+        <v>-55.36929399999998</v>
       </c>
       <c r="O31">
-        <v>-11.531186524</v>
+        <v>-12.18124468</v>
       </c>
       <c r="P31">
-        <v>-40.88329767599999</v>
+        <v>-43.18804931999999</v>
       </c>
       <c r="Q31">
-        <v>54.216702324</v>
+        <v>51.91195068</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1039161894725493</v>
+        <v>0.1047464207507285</v>
       </c>
       <c r="T31">
-        <v>1.342175276502293</v>
+        <v>1.361349209023754</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08543055274920189</v>
+        <v>0.08258286765756183</v>
       </c>
       <c r="W31">
-        <v>0.2156554756617382</v>
+        <v>0.2163269598063469</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3883206943145541</v>
+        <v>0.3753766711707356</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.138220582467414</v>
+        <v>0.140120582467414</v>
       </c>
       <c r="C32">
-        <v>121.8992956558014</v>
+        <v>99.64819387353367</v>
       </c>
       <c r="D32">
-        <v>482.5292956558013</v>
+        <v>472.8091938735336</v>
       </c>
       <c r="E32">
-        <v>-159.47</v>
+        <v>-146.939</v>
       </c>
       <c r="F32">
-        <v>375.9299999999999</v>
+        <v>388.461</v>
       </c>
       <c r="G32">
         <v>15.3</v>
@@ -3917,37 +3917,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M32">
-        <v>88.64429399999999</v>
+        <v>91.59910379999999</v>
       </c>
       <c r="N32">
-        <v>-55.36929399999998</v>
+        <v>-58.32410379999999</v>
       </c>
       <c r="O32">
-        <v>-12.18124468</v>
+        <v>-12.831302836</v>
       </c>
       <c r="P32">
-        <v>-43.18804931999999</v>
+        <v>-45.49280096399999</v>
       </c>
       <c r="Q32">
-        <v>51.91195068</v>
+        <v>49.607199036</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1047464207507285</v>
+        <v>0.1056007167036376</v>
       </c>
       <c r="T32">
-        <v>1.361349209023754</v>
+        <v>1.381078907705258</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08258286765756183</v>
+        <v>0.07991890418473725</v>
       </c>
       <c r="W32">
-        <v>0.2163269598063469</v>
+        <v>0.216955122393239</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3753766711707356</v>
+        <v>0.3632677462942602</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.140120582467414</v>
+        <v>0.1420205824674141</v>
       </c>
       <c r="C33">
-        <v>99.64819387353367</v>
+        <v>77.78096408440365</v>
       </c>
       <c r="D33">
-        <v>472.8091938735336</v>
+        <v>463.4729640844036</v>
       </c>
       <c r="E33">
-        <v>-146.939</v>
+        <v>-134.408</v>
       </c>
       <c r="F33">
-        <v>388.461</v>
+        <v>400.992</v>
       </c>
       <c r="G33">
         <v>15.3</v>
@@ -3999,37 +3999,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M33">
-        <v>91.59910379999999</v>
+        <v>94.5539136</v>
       </c>
       <c r="N33">
-        <v>-58.32410379999999</v>
+        <v>-61.2789136</v>
       </c>
       <c r="O33">
-        <v>-12.831302836</v>
+        <v>-13.481360992</v>
       </c>
       <c r="P33">
-        <v>-45.49280096399999</v>
+        <v>-47.797552608</v>
       </c>
       <c r="Q33">
-        <v>49.607199036</v>
+        <v>47.302447392</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1056007167036376</v>
+        <v>0.1064801390081029</v>
       </c>
       <c r="T33">
-        <v>1.381078907705258</v>
+        <v>1.4013888916421</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.07991890418473725</v>
+        <v>0.07742143842896421</v>
       </c>
       <c r="W33">
-        <v>0.216955122393239</v>
+        <v>0.2175440248184503</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3632677462942602</v>
+        <v>0.3519156292225646</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1420205824674141</v>
+        <v>0.1439205824674141</v>
       </c>
       <c r="C34">
-        <v>77.78096408440365</v>
+        <v>56.27530647826052</v>
       </c>
       <c r="D34">
-        <v>463.4729640844036</v>
+        <v>454.4983064782605</v>
       </c>
       <c r="E34">
-        <v>-134.408</v>
+        <v>-121.877</v>
       </c>
       <c r="F34">
-        <v>400.992</v>
+        <v>413.523</v>
       </c>
       <c r="G34">
         <v>15.3</v>
@@ -4081,37 +4081,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M34">
-        <v>94.5539136</v>
+        <v>97.50872339999999</v>
       </c>
       <c r="N34">
-        <v>-61.2789136</v>
+        <v>-64.23372339999999</v>
       </c>
       <c r="O34">
-        <v>-13.481360992</v>
+        <v>-14.131419148</v>
       </c>
       <c r="P34">
-        <v>-47.797552608</v>
+        <v>-50.10230425199999</v>
       </c>
       <c r="Q34">
-        <v>47.302447392</v>
+        <v>44.99769574800001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064801390081029</v>
+        <v>0.1073858127246418</v>
       </c>
       <c r="T34">
-        <v>1.4013888916421</v>
+        <v>1.422305143756161</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07742143842896421</v>
+        <v>0.07507533423414711</v>
       </c>
       <c r="W34">
-        <v>0.2175440248184503</v>
+        <v>0.2180972361875881</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3519156292225646</v>
+        <v>0.3412515192461233</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1439205824674141</v>
+        <v>0.145820582467414</v>
       </c>
       <c r="C35">
-        <v>56.27530647826052</v>
+        <v>35.11061568176842</v>
       </c>
       <c r="D35">
-        <v>454.4983064782605</v>
+        <v>445.8646156817684</v>
       </c>
       <c r="E35">
-        <v>-121.877</v>
+        <v>-109.346</v>
       </c>
       <c r="F35">
-        <v>413.523</v>
+        <v>426.054</v>
       </c>
       <c r="G35">
         <v>15.3</v>
@@ -4163,37 +4163,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M35">
-        <v>97.50872339999999</v>
+        <v>100.4635332</v>
       </c>
       <c r="N35">
-        <v>-64.23372339999999</v>
+        <v>-67.18853319999999</v>
       </c>
       <c r="O35">
-        <v>-14.131419148</v>
+        <v>-14.781477304</v>
       </c>
       <c r="P35">
-        <v>-50.10230425199999</v>
+        <v>-52.407055896</v>
       </c>
       <c r="Q35">
-        <v>44.99769574800001</v>
+        <v>42.692944104</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1073858127246418</v>
+        <v>0.1083189310992575</v>
       </c>
       <c r="T35">
-        <v>1.422305143756161</v>
+        <v>1.44385522169186</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07507533423414711</v>
+        <v>0.07286723616843689</v>
       </c>
       <c r="W35">
-        <v>0.2180972361875881</v>
+        <v>0.2186179057114826</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3412515192461233</v>
+        <v>0.3312147098565313</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.145820582467414</v>
+        <v>0.147720582467414</v>
       </c>
       <c r="C36">
-        <v>35.11061568176842</v>
+        <v>14.26782282024101</v>
       </c>
       <c r="D36">
-        <v>445.8646156817684</v>
+        <v>437.552822820241</v>
       </c>
       <c r="E36">
-        <v>-109.346</v>
+        <v>-96.81499999999994</v>
       </c>
       <c r="F36">
-        <v>426.054</v>
+        <v>438.585</v>
       </c>
       <c r="G36">
         <v>15.3</v>
@@ -4245,37 +4245,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M36">
-        <v>100.4635332</v>
+        <v>103.418343</v>
       </c>
       <c r="N36">
-        <v>-67.18853319999999</v>
+        <v>-70.143343</v>
       </c>
       <c r="O36">
-        <v>-14.781477304</v>
+        <v>-15.43153546</v>
       </c>
       <c r="P36">
-        <v>-52.407055896</v>
+        <v>-54.71180754</v>
       </c>
       <c r="Q36">
-        <v>42.692944104</v>
+        <v>40.38819245999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1083189310992575</v>
+        <v>0.1092807608084769</v>
       </c>
       <c r="T36">
-        <v>1.44385522169186</v>
+        <v>1.466068378948658</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07286723616843689</v>
+        <v>0.07078531513505298</v>
       </c>
       <c r="W36">
-        <v>0.2186179057114826</v>
+        <v>0.2191088226911545</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3312147098565313</v>
+        <v>0.3217514324320591</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.147720582467414</v>
+        <v>0.1496205824674141</v>
       </c>
       <c r="C37">
-        <v>14.26782282024101</v>
+        <v>-6.270745078151322</v>
       </c>
       <c r="D37">
-        <v>437.552822820241</v>
+        <v>429.5452549218487</v>
       </c>
       <c r="E37">
-        <v>-96.81499999999994</v>
+        <v>-84.28399999999993</v>
       </c>
       <c r="F37">
-        <v>438.585</v>
+        <v>451.116</v>
       </c>
       <c r="G37">
         <v>15.3</v>
@@ -4327,37 +4327,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M37">
-        <v>103.418343</v>
+        <v>106.3731528</v>
       </c>
       <c r="N37">
-        <v>-70.143343</v>
+        <v>-73.09815280000001</v>
       </c>
       <c r="O37">
-        <v>-15.43153546</v>
+        <v>-16.081593616</v>
       </c>
       <c r="P37">
-        <v>-54.71180754</v>
+        <v>-57.016559184</v>
       </c>
       <c r="Q37">
-        <v>40.38819245999999</v>
+        <v>38.08344081599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1092807608084769</v>
+        <v>0.1102726476961093</v>
       </c>
       <c r="T37">
-        <v>1.466068378948658</v>
+        <v>1.488975697369731</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07078531513505298</v>
+        <v>0.06881905638130151</v>
       </c>
       <c r="W37">
-        <v>0.2191088226911545</v>
+        <v>0.2195724665052891</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3217514324320591</v>
+        <v>0.3128138926422795</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1496205824674141</v>
+        <v>0.1515205824674141</v>
       </c>
       <c r="C38">
-        <v>-6.270745078151208</v>
+        <v>-26.52149051753219</v>
       </c>
       <c r="D38">
-        <v>429.5452549218487</v>
+        <v>421.8255094824677</v>
       </c>
       <c r="E38">
-        <v>-84.28400000000005</v>
+        <v>-71.75300000000004</v>
       </c>
       <c r="F38">
-        <v>451.1159999999999</v>
+        <v>463.6469999999999</v>
       </c>
       <c r="G38">
         <v>15.3</v>
@@ -4409,37 +4409,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M38">
-        <v>106.3731528</v>
+        <v>109.3279626</v>
       </c>
       <c r="N38">
-        <v>-73.09815279999998</v>
+        <v>-76.05296259999999</v>
       </c>
       <c r="O38">
-        <v>-16.081593616</v>
+        <v>-16.731651772</v>
       </c>
       <c r="P38">
-        <v>-57.01655918399999</v>
+        <v>-59.32131082799999</v>
       </c>
       <c r="Q38">
-        <v>38.08344081600001</v>
+        <v>35.778689172</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1102726476961093</v>
+        <v>0.111296023056365</v>
       </c>
       <c r="T38">
-        <v>1.488975697369731</v>
+        <v>1.512610232248616</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.06881905638130152</v>
+        <v>0.06695908188450959</v>
       </c>
       <c r="W38">
-        <v>0.2195724665052891</v>
+        <v>0.2200110484916326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3128138926422797</v>
+        <v>0.3043594631114073</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1515205824674141</v>
+        <v>0.1534205824674141</v>
       </c>
       <c r="C39">
-        <v>-26.52149051753219</v>
+        <v>-46.49965768241327</v>
       </c>
       <c r="D39">
-        <v>421.8255094824677</v>
+        <v>414.3783423175867</v>
       </c>
       <c r="E39">
-        <v>-71.75300000000004</v>
+        <v>-59.22199999999998</v>
       </c>
       <c r="F39">
-        <v>463.6469999999999</v>
+        <v>476.178</v>
       </c>
       <c r="G39">
         <v>15.3</v>
@@ -4491,37 +4491,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M39">
-        <v>109.3279626</v>
+        <v>112.2827724</v>
       </c>
       <c r="N39">
-        <v>-76.05296259999999</v>
+        <v>-79.00777239999999</v>
       </c>
       <c r="O39">
-        <v>-16.731651772</v>
+        <v>-17.381709928</v>
       </c>
       <c r="P39">
-        <v>-59.32131082799999</v>
+        <v>-61.62606247199999</v>
       </c>
       <c r="Q39">
-        <v>35.778689172</v>
+        <v>33.473937528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.111296023056365</v>
+        <v>0.1123524105250161</v>
       </c>
       <c r="T39">
-        <v>1.512610232248616</v>
+        <v>1.537007171478432</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06695908188450959</v>
+        <v>0.06519700078228564</v>
       </c>
       <c r="W39">
-        <v>0.2200110484916326</v>
+        <v>0.2204265472155371</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3043594631114073</v>
+        <v>0.2963500035558438</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1534205824674141</v>
+        <v>0.155320582467414</v>
       </c>
       <c r="C40">
-        <v>-46.49965768241327</v>
+        <v>-66.21943291228973</v>
       </c>
       <c r="D40">
-        <v>414.3783423175867</v>
+        <v>407.1895670877103</v>
       </c>
       <c r="E40">
-        <v>-59.22199999999998</v>
+        <v>-46.69099999999997</v>
       </c>
       <c r="F40">
-        <v>476.178</v>
+        <v>488.709</v>
       </c>
       <c r="G40">
         <v>15.3</v>
@@ -4573,37 +4573,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M40">
-        <v>112.2827724</v>
+        <v>115.2375822</v>
       </c>
       <c r="N40">
-        <v>-79.00777239999999</v>
+        <v>-81.9625822</v>
       </c>
       <c r="O40">
-        <v>-17.381709928</v>
+        <v>-18.031768084</v>
       </c>
       <c r="P40">
-        <v>-61.62606247199999</v>
+        <v>-63.930814116</v>
       </c>
       <c r="Q40">
-        <v>33.473937528</v>
+        <v>31.16918588399999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1123524105250161</v>
+        <v>0.113443433648377</v>
       </c>
       <c r="T40">
-        <v>1.537007171478432</v>
+        <v>1.562204010355128</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06519700078228564</v>
+        <v>0.0635252828135091</v>
       </c>
       <c r="W40">
-        <v>0.2204265472155371</v>
+        <v>0.2208207383125746</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2963500035558438</v>
+        <v>0.2887512855159504</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.155320582467414</v>
+        <v>0.157220582467414</v>
       </c>
       <c r="C41">
-        <v>-66.21943291228973</v>
+        <v>-85.69403489617747</v>
       </c>
       <c r="D41">
-        <v>407.1895670877103</v>
+        <v>400.2459651038225</v>
       </c>
       <c r="E41">
-        <v>-46.69099999999997</v>
+        <v>-34.15999999999997</v>
       </c>
       <c r="F41">
-        <v>488.709</v>
+        <v>501.24</v>
       </c>
       <c r="G41">
         <v>15.3</v>
@@ -4655,37 +4655,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M41">
-        <v>115.2375822</v>
+        <v>118.192392</v>
       </c>
       <c r="N41">
-        <v>-81.9625822</v>
+        <v>-84.91739200000001</v>
       </c>
       <c r="O41">
-        <v>-18.031768084</v>
+        <v>-18.68182624</v>
       </c>
       <c r="P41">
-        <v>-63.930814116</v>
+        <v>-66.23556576</v>
       </c>
       <c r="Q41">
-        <v>31.16918588399999</v>
+        <v>28.86443423999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.113443433648377</v>
+        <v>0.1145708242091833</v>
       </c>
       <c r="T41">
-        <v>1.562204010355128</v>
+        <v>1.588240743861046</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0635252828135091</v>
+        <v>0.06193715074317136</v>
       </c>
       <c r="W41">
-        <v>0.2208207383125746</v>
+        <v>0.2211952198547602</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2887512855159504</v>
+        <v>0.2815325033780516</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.157220582467414</v>
+        <v>0.1591205824674141</v>
       </c>
       <c r="C42">
-        <v>-85.69403489617747</v>
+        <v>-104.9357957936158</v>
       </c>
       <c r="D42">
-        <v>400.2459651038225</v>
+        <v>393.5352042063842</v>
       </c>
       <c r="E42">
-        <v>-34.15999999999997</v>
+        <v>-21.62900000000002</v>
       </c>
       <c r="F42">
-        <v>501.24</v>
+        <v>513.771</v>
       </c>
       <c r="G42">
         <v>15.3</v>
@@ -4737,37 +4737,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M42">
-        <v>118.192392</v>
+        <v>121.1472018</v>
       </c>
       <c r="N42">
-        <v>-84.91739200000001</v>
+        <v>-87.87220179999998</v>
       </c>
       <c r="O42">
-        <v>-18.68182624</v>
+        <v>-19.331884396</v>
       </c>
       <c r="P42">
-        <v>-66.23556576</v>
+        <v>-68.54031740399999</v>
       </c>
       <c r="Q42">
-        <v>28.86443423999999</v>
+        <v>26.559682596</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1145708242091833</v>
+        <v>0.1157364313991694</v>
       </c>
       <c r="T42">
-        <v>1.588240743861046</v>
+        <v>1.615160078502759</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06193715074317136</v>
+        <v>0.06042648852992329</v>
       </c>
       <c r="W42">
-        <v>0.2211952198547602</v>
+        <v>0.2215514340046441</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2815325033780516</v>
+        <v>0.2746658569541968</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1591205824674141</v>
+        <v>0.1610205824674141</v>
       </c>
       <c r="C43">
-        <v>-104.9357957936158</v>
+        <v>-123.9562343295094</v>
       </c>
       <c r="D43">
-        <v>393.5352042063842</v>
+        <v>387.0457656704907</v>
       </c>
       <c r="E43">
-        <v>-21.62900000000002</v>
+        <v>-9.097999999999956</v>
       </c>
       <c r="F43">
-        <v>513.771</v>
+        <v>526.302</v>
       </c>
       <c r="G43">
         <v>15.3</v>
@@ -4819,37 +4819,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M43">
-        <v>121.1472018</v>
+        <v>124.1020116</v>
       </c>
       <c r="N43">
-        <v>-87.87220179999998</v>
+        <v>-90.82701160000001</v>
       </c>
       <c r="O43">
-        <v>-19.331884396</v>
+        <v>-19.981942552</v>
       </c>
       <c r="P43">
-        <v>-68.54031740399999</v>
+        <v>-70.845069048</v>
       </c>
       <c r="Q43">
-        <v>26.559682596</v>
+        <v>24.254930952</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1157364313991694</v>
+        <v>0.1169422319405344</v>
       </c>
       <c r="T43">
-        <v>1.615160078502759</v>
+        <v>1.643007666063151</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06042648852992329</v>
+        <v>0.05898776261254416</v>
       </c>
       <c r="W43">
-        <v>0.2215514340046441</v>
+        <v>0.2218906855759621</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2746658569541968</v>
+        <v>0.2681261936933825</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1610205824674141</v>
+        <v>0.1629205824674141</v>
       </c>
       <c r="C44">
-        <v>-123.9562343295092</v>
+        <v>-142.7661217742378</v>
       </c>
       <c r="D44">
-        <v>387.0457656704907</v>
+        <v>380.7668782257622</v>
       </c>
       <c r="E44">
-        <v>-9.09800000000007</v>
+        <v>3.432999999999993</v>
       </c>
       <c r="F44">
-        <v>526.3019999999999</v>
+        <v>538.833</v>
       </c>
       <c r="G44">
         <v>15.3</v>
@@ -4901,37 +4901,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M44">
-        <v>124.1020116</v>
+        <v>127.0568214</v>
       </c>
       <c r="N44">
-        <v>-90.82701159999998</v>
+        <v>-93.7818214</v>
       </c>
       <c r="O44">
-        <v>-19.981942552</v>
+        <v>-20.632000708</v>
       </c>
       <c r="P44">
-        <v>-70.84506904799998</v>
+        <v>-73.14982069199999</v>
       </c>
       <c r="Q44">
-        <v>24.25493095200001</v>
+        <v>21.950179308</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1169422319405344</v>
+        <v>0.1181903412728245</v>
       </c>
       <c r="T44">
-        <v>1.643007666063151</v>
+        <v>1.671832361958996</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05898776261254417</v>
+        <v>0.05761595417969429</v>
       </c>
       <c r="W44">
-        <v>0.2218906855759621</v>
+        <v>0.2222141580044281</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2681261936933825</v>
+        <v>0.2618907008167922</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1629205824674141</v>
+        <v>0.164820582467414</v>
       </c>
       <c r="C45">
-        <v>-142.7661217742378</v>
+        <v>-161.3755416040769</v>
       </c>
       <c r="D45">
-        <v>380.7668782257622</v>
+        <v>374.688458395923</v>
       </c>
       <c r="E45">
-        <v>3.432999999999993</v>
+        <v>15.96399999999994</v>
       </c>
       <c r="F45">
-        <v>538.833</v>
+        <v>551.3639999999999</v>
       </c>
       <c r="G45">
         <v>15.3</v>
@@ -4983,37 +4983,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M45">
-        <v>127.0568214</v>
+        <v>130.0116312</v>
       </c>
       <c r="N45">
-        <v>-93.7818214</v>
+        <v>-96.73663119999998</v>
       </c>
       <c r="O45">
-        <v>-20.632000708</v>
+        <v>-21.282058864</v>
       </c>
       <c r="P45">
-        <v>-73.14982069199999</v>
+        <v>-75.45457233599998</v>
       </c>
       <c r="Q45">
-        <v>21.950179308</v>
+        <v>19.64542766400001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1181903412728245</v>
+        <v>0.1194830259384107</v>
       </c>
       <c r="T45">
-        <v>1.671832361958996</v>
+        <v>1.701686511279693</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05761595417969429</v>
+        <v>0.05630650067561033</v>
       </c>
       <c r="W45">
-        <v>0.2222141580044281</v>
+        <v>0.2225229271406911</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2618907008167922</v>
+        <v>0.2559386394345925</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.164820582467414</v>
+        <v>0.1667205824674141</v>
       </c>
       <c r="C46">
-        <v>-161.3755416040769</v>
+        <v>-179.7939435370284</v>
       </c>
       <c r="D46">
-        <v>374.688458395923</v>
+        <v>368.8010564629716</v>
       </c>
       <c r="E46">
-        <v>15.96399999999994</v>
+        <v>28.495</v>
       </c>
       <c r="F46">
-        <v>551.3639999999999</v>
+        <v>563.895</v>
       </c>
       <c r="G46">
         <v>15.3</v>
@@ -5065,37 +5065,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M46">
-        <v>130.0116312</v>
+        <v>132.966441</v>
       </c>
       <c r="N46">
-        <v>-96.73663119999998</v>
+        <v>-99.691441</v>
       </c>
       <c r="O46">
-        <v>-21.282058864</v>
+        <v>-21.93211702</v>
       </c>
       <c r="P46">
-        <v>-75.45457233599998</v>
+        <v>-77.75932398</v>
       </c>
       <c r="Q46">
-        <v>19.64542766400001</v>
+        <v>17.34067601999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1194830259384107</v>
+        <v>0.120822717319109</v>
       </c>
       <c r="T46">
-        <v>1.701686511279693</v>
+        <v>1.732626266030232</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05630650067561033</v>
+        <v>0.05505524510504121</v>
       </c>
       <c r="W46">
-        <v>0.2225229271406911</v>
+        <v>0.2228179732042313</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2559386394345925</v>
+        <v>0.2502511141138237</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1667205824674141</v>
+        <v>0.1686205824674141</v>
       </c>
       <c r="C47">
-        <v>-179.7939435370284</v>
+        <v>-198.0301925531333</v>
       </c>
       <c r="D47">
-        <v>368.8010564629716</v>
+        <v>363.0958074468666</v>
       </c>
       <c r="E47">
-        <v>28.495</v>
+        <v>41.02599999999995</v>
       </c>
       <c r="F47">
-        <v>563.895</v>
+        <v>576.4259999999999</v>
       </c>
       <c r="G47">
         <v>15.3</v>
@@ -5147,37 +5147,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M47">
-        <v>132.966441</v>
+        <v>135.9212508</v>
       </c>
       <c r="N47">
-        <v>-99.691441</v>
+        <v>-102.6462508</v>
       </c>
       <c r="O47">
-        <v>-21.93211702</v>
+        <v>-22.582175176</v>
       </c>
       <c r="P47">
-        <v>-77.75932398</v>
+        <v>-80.064075624</v>
       </c>
       <c r="Q47">
-        <v>17.34067601999999</v>
+        <v>15.035924376</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.120822717319109</v>
+        <v>0.1222120268990926</v>
       </c>
       <c r="T47">
-        <v>1.732626266030232</v>
+        <v>1.764711937623385</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05505524510504121</v>
+        <v>0.0538583919505838</v>
       </c>
       <c r="W47">
-        <v>0.2228179732042313</v>
+        <v>0.2231001911780523</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2502511141138237</v>
+        <v>0.2448108725026537</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1686205824674141</v>
+        <v>0.1705205824674141</v>
       </c>
       <c r="C48">
-        <v>-198.0301925531333</v>
+        <v>-216.0926134341198</v>
       </c>
       <c r="D48">
-        <v>363.0958074468666</v>
+        <v>357.5643865658802</v>
       </c>
       <c r="E48">
-        <v>41.02599999999995</v>
+        <v>53.55700000000002</v>
       </c>
       <c r="F48">
-        <v>576.4259999999999</v>
+        <v>588.957</v>
       </c>
       <c r="G48">
         <v>15.3</v>
@@ -5229,37 +5229,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M48">
-        <v>135.9212508</v>
+        <v>138.8760606</v>
       </c>
       <c r="N48">
-        <v>-102.6462508</v>
+        <v>-105.6010606</v>
       </c>
       <c r="O48">
-        <v>-22.582175176</v>
+        <v>-23.232233332</v>
       </c>
       <c r="P48">
-        <v>-80.064075624</v>
+        <v>-82.368827268</v>
       </c>
       <c r="Q48">
-        <v>15.035924376</v>
+        <v>12.73117273199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1222120268990926</v>
+        <v>0.1236537632556792</v>
       </c>
       <c r="T48">
-        <v>1.764711937623385</v>
+        <v>1.798008389276656</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0538583919505838</v>
+        <v>0.05271246871759264</v>
       </c>
       <c r="W48">
-        <v>0.2231001911780523</v>
+        <v>0.2233703998763917</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2448108725026537</v>
+        <v>0.2396021305345121</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1705205824674141</v>
+        <v>0.1724205824674141</v>
       </c>
       <c r="C49">
-        <v>-216.0926134341198</v>
+        <v>-233.9890312930215</v>
       </c>
       <c r="D49">
-        <v>357.5643865658802</v>
+        <v>352.1989687069786</v>
       </c>
       <c r="E49">
-        <v>53.55700000000002</v>
+        <v>66.08800000000008</v>
       </c>
       <c r="F49">
-        <v>588.957</v>
+        <v>601.4880000000001</v>
       </c>
       <c r="G49">
         <v>15.3</v>
@@ -5311,37 +5311,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M49">
-        <v>138.8760606</v>
+        <v>141.8308704</v>
       </c>
       <c r="N49">
-        <v>-105.6010606</v>
+        <v>-108.5558704</v>
       </c>
       <c r="O49">
-        <v>-23.232233332</v>
+        <v>-23.882291488</v>
       </c>
       <c r="P49">
-        <v>-82.368827268</v>
+        <v>-84.67357891200001</v>
       </c>
       <c r="Q49">
-        <v>12.73117273199999</v>
+        <v>10.42642108799998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1236537632556792</v>
+        <v>0.1251509510105961</v>
       </c>
       <c r="T49">
-        <v>1.798008389276656</v>
+        <v>1.832585473685823</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05271246871759264</v>
+        <v>0.05161429228597613</v>
       </c>
       <c r="W49">
-        <v>0.2233703998763917</v>
+        <v>0.2236293498789668</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2396021305345121</v>
+        <v>0.2346104194817097</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1724205824674141</v>
+        <v>0.1743205824674141</v>
       </c>
       <c r="C50">
-        <v>-233.9890312930212</v>
+        <v>-251.7268085087478</v>
       </c>
       <c r="D50">
-        <v>352.1989687069787</v>
+        <v>346.9921914912521</v>
       </c>
       <c r="E50">
-        <v>66.08799999999997</v>
+        <v>78.61899999999991</v>
       </c>
       <c r="F50">
-        <v>601.4879999999999</v>
+        <v>614.0189999999999</v>
       </c>
       <c r="G50">
         <v>15.3</v>
@@ -5393,37 +5393,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M50">
-        <v>141.8308704</v>
+        <v>144.7856802</v>
       </c>
       <c r="N50">
-        <v>-108.5558704</v>
+        <v>-111.5106802</v>
       </c>
       <c r="O50">
-        <v>-23.882291488</v>
+        <v>-24.53234964399999</v>
       </c>
       <c r="P50">
-        <v>-84.67357891199998</v>
+        <v>-86.97833055599997</v>
       </c>
       <c r="Q50">
-        <v>10.42642108800001</v>
+        <v>8.12166944400002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1251509510105961</v>
+        <v>0.1267068520108039</v>
       </c>
       <c r="T50">
-        <v>1.832585473685823</v>
+        <v>1.868518522189466</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05161429228597614</v>
+        <v>0.05056093938218072</v>
       </c>
       <c r="W50">
-        <v>0.2236293498789668</v>
+        <v>0.2238777304936818</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2346104194817098</v>
+        <v>0.2298224517371851</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1743205824674141</v>
+        <v>0.1762205824674141</v>
       </c>
       <c r="C51">
-        <v>-251.7268085087478</v>
+        <v>-269.3128784322249</v>
       </c>
       <c r="D51">
-        <v>346.9921914912521</v>
+        <v>341.937121567775</v>
       </c>
       <c r="E51">
-        <v>78.61899999999991</v>
+        <v>91.14999999999998</v>
       </c>
       <c r="F51">
-        <v>614.0189999999999</v>
+        <v>626.55</v>
       </c>
       <c r="G51">
         <v>15.3</v>
@@ -5475,37 +5475,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M51">
-        <v>144.7856802</v>
+        <v>147.74049</v>
       </c>
       <c r="N51">
-        <v>-111.5106802</v>
+        <v>-114.46549</v>
       </c>
       <c r="O51">
-        <v>-24.53234964399999</v>
+        <v>-25.1824078</v>
       </c>
       <c r="P51">
-        <v>-86.97833055599997</v>
+        <v>-89.2830822</v>
       </c>
       <c r="Q51">
-        <v>8.12166944400002</v>
+        <v>5.816917799999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1267068520108039</v>
+        <v>0.1283249890510199</v>
       </c>
       <c r="T51">
-        <v>1.868518522189466</v>
+        <v>1.905888892633255</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05056093938218072</v>
+        <v>0.04954972059453709</v>
       </c>
       <c r="W51">
-        <v>0.2238777304936818</v>
+        <v>0.2241161758838082</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2298224517371851</v>
+        <v>0.2252260027024413</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1762205824674141</v>
+        <v>0.1781205824674141</v>
       </c>
       <c r="C52">
-        <v>-269.3128784322249</v>
+        <v>-286.7537761885985</v>
       </c>
       <c r="D52">
-        <v>341.937121567775</v>
+        <v>337.0272238114015</v>
       </c>
       <c r="E52">
-        <v>91.14999999999998</v>
+        <v>103.681</v>
       </c>
       <c r="F52">
-        <v>626.55</v>
+        <v>639.081</v>
       </c>
       <c r="G52">
         <v>15.3</v>
@@ -5557,37 +5557,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M52">
-        <v>147.74049</v>
+        <v>150.6952998</v>
       </c>
       <c r="N52">
-        <v>-114.46549</v>
+        <v>-117.4202998</v>
       </c>
       <c r="O52">
-        <v>-25.1824078</v>
+        <v>-25.832465956</v>
       </c>
       <c r="P52">
-        <v>-89.2830822</v>
+        <v>-91.587833844</v>
       </c>
       <c r="Q52">
-        <v>5.816917799999999</v>
+        <v>3.512166155999992</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1283249890510199</v>
+        <v>0.1300091725010408</v>
       </c>
       <c r="T52">
-        <v>1.905888892633255</v>
+        <v>1.944784584319649</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04954972059453709</v>
+        <v>0.0485781574456246</v>
       </c>
       <c r="W52">
-        <v>0.2241161758838082</v>
+        <v>0.2243452704743217</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2252260027024413</v>
+        <v>0.2208098065710209</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1781205824674141</v>
+        <v>0.1800205824674141</v>
       </c>
       <c r="C53">
-        <v>-286.7537761885985</v>
+        <v>-304.0556668632616</v>
       </c>
       <c r="D53">
-        <v>337.0272238114015</v>
+        <v>332.2563331367383</v>
       </c>
       <c r="E53">
-        <v>103.681</v>
+        <v>116.212</v>
       </c>
       <c r="F53">
-        <v>639.081</v>
+        <v>651.612</v>
       </c>
       <c r="G53">
         <v>15.3</v>
@@ -5639,37 +5639,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M53">
-        <v>150.6952998</v>
+        <v>153.6501096</v>
       </c>
       <c r="N53">
-        <v>-117.4202998</v>
+        <v>-120.3751096</v>
       </c>
       <c r="O53">
-        <v>-25.832465956</v>
+        <v>-26.482524112</v>
       </c>
       <c r="P53">
-        <v>-91.587833844</v>
+        <v>-93.89258548800001</v>
       </c>
       <c r="Q53">
-        <v>3.512166155999992</v>
+        <v>1.207414511999986</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1300091725010408</v>
+        <v>0.1317635302614791</v>
       </c>
       <c r="T53">
-        <v>1.944784584319649</v>
+        <v>1.985300929826308</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0485781574456246</v>
+        <v>0.04764396211013182</v>
       </c>
       <c r="W53">
-        <v>0.2243452704743217</v>
+        <v>0.2245655537344309</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2208098065710209</v>
+        <v>0.2165634641369628</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1800205824674141</v>
+        <v>0.1819205824674141</v>
       </c>
       <c r="C54">
-        <v>-304.0556668632616</v>
+        <v>-321.2243713273234</v>
       </c>
       <c r="D54">
-        <v>332.2563331367383</v>
+        <v>327.6186286726766</v>
       </c>
       <c r="E54">
-        <v>116.212</v>
+        <v>128.7430000000001</v>
       </c>
       <c r="F54">
-        <v>651.612</v>
+        <v>664.143</v>
       </c>
       <c r="G54">
         <v>15.3</v>
@@ -5721,37 +5721,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M54">
-        <v>153.6501096</v>
+        <v>156.6049194</v>
       </c>
       <c r="N54">
-        <v>-120.3751096</v>
+        <v>-123.3299194</v>
       </c>
       <c r="O54">
-        <v>-26.482524112</v>
+        <v>-27.132582268</v>
       </c>
       <c r="P54">
-        <v>-93.89258548800001</v>
+        <v>-96.197337132</v>
       </c>
       <c r="Q54">
-        <v>1.207414511999986</v>
+        <v>-1.097337132000007</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1317635302614791</v>
+        <v>0.1335925415436383</v>
       </c>
       <c r="T54">
-        <v>1.985300929826308</v>
+        <v>2.027541375141761</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04764396211013182</v>
+        <v>0.04674501942880858</v>
       </c>
       <c r="W54">
-        <v>0.2245655537344309</v>
+        <v>0.224777524418687</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2165634641369628</v>
+        <v>0.212477361040039</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1819205824674141</v>
+        <v>0.1838205824674141</v>
       </c>
       <c r="C55">
-        <v>-321.2243713273234</v>
+        <v>-338.2653899299839</v>
       </c>
       <c r="D55">
-        <v>327.6186286726766</v>
+        <v>323.108610070016</v>
       </c>
       <c r="E55">
-        <v>128.7430000000001</v>
+        <v>141.274</v>
       </c>
       <c r="F55">
-        <v>664.143</v>
+        <v>676.674</v>
       </c>
       <c r="G55">
         <v>15.3</v>
@@ -5803,37 +5803,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M55">
-        <v>156.6049194</v>
+        <v>159.5597292</v>
       </c>
       <c r="N55">
-        <v>-123.3299194</v>
+        <v>-126.2847292</v>
       </c>
       <c r="O55">
-        <v>-27.132582268</v>
+        <v>-27.782640424</v>
       </c>
       <c r="P55">
-        <v>-96.197337132</v>
+        <v>-98.50208877599999</v>
       </c>
       <c r="Q55">
-        <v>-1.097337132000007</v>
+        <v>-3.402088775999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1335925415436383</v>
+        <v>0.1355010750554565</v>
       </c>
       <c r="T55">
-        <v>2.027541375141761</v>
+        <v>2.071618361557887</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04674501942880858</v>
+        <v>0.04587937092086768</v>
       </c>
       <c r="W55">
-        <v>0.224777524418687</v>
+        <v>0.2249816443368594</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.212477361040039</v>
+        <v>0.2085425950948531</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1838205824674141</v>
+        <v>0.1857205824674141</v>
       </c>
       <c r="C56">
-        <v>-338.2653899299839</v>
+        <v>-355.1839242605819</v>
       </c>
       <c r="D56">
-        <v>323.108610070016</v>
+        <v>318.7210757394182</v>
       </c>
       <c r="E56">
-        <v>141.274</v>
+        <v>153.8050000000001</v>
       </c>
       <c r="F56">
-        <v>676.674</v>
+        <v>689.205</v>
       </c>
       <c r="G56">
         <v>15.3</v>
@@ -5885,37 +5885,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M56">
-        <v>159.5597292</v>
+        <v>162.514539</v>
       </c>
       <c r="N56">
-        <v>-126.2847292</v>
+        <v>-129.239539</v>
       </c>
       <c r="O56">
-        <v>-27.782640424</v>
+        <v>-28.43269858</v>
       </c>
       <c r="P56">
-        <v>-98.50208877599999</v>
+        <v>-100.80684042</v>
       </c>
       <c r="Q56">
-        <v>-3.402088775999999</v>
+        <v>-5.70684042000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1355010750554565</v>
+        <v>0.1374944322789111</v>
       </c>
       <c r="T56">
-        <v>2.071618361557887</v>
+        <v>2.117654325148062</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04587937092086768</v>
+        <v>0.04504520054048826</v>
       </c>
       <c r="W56">
-        <v>0.2249816443368594</v>
+        <v>0.2251783417125529</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2085425950948531</v>
+        <v>0.2047509115476739</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1857205824674141</v>
+        <v>0.1876205824674141</v>
       </c>
       <c r="C57">
-        <v>-355.1839242605819</v>
+        <v>-371.984897161335</v>
       </c>
       <c r="D57">
-        <v>318.7210757394182</v>
+        <v>314.451102838665</v>
       </c>
       <c r="E57">
-        <v>153.8050000000001</v>
+        <v>166.336</v>
       </c>
       <c r="F57">
-        <v>689.205</v>
+        <v>701.736</v>
       </c>
       <c r="G57">
         <v>15.3</v>
@@ -5967,37 +5967,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M57">
-        <v>162.514539</v>
+        <v>165.4693488</v>
       </c>
       <c r="N57">
-        <v>-129.239539</v>
+        <v>-132.1943488</v>
       </c>
       <c r="O57">
-        <v>-28.43269858</v>
+        <v>-29.082756736</v>
       </c>
       <c r="P57">
-        <v>-100.80684042</v>
+        <v>-103.111592064</v>
       </c>
       <c r="Q57">
-        <v>-5.70684042000002</v>
+        <v>-8.011592064000013</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1374944322789111</v>
+        <v>0.1395783966488863</v>
       </c>
       <c r="T57">
-        <v>2.117654325148062</v>
+        <v>2.165782832537791</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04504520054048826</v>
+        <v>0.04424082195940812</v>
       </c>
       <c r="W57">
-        <v>0.2251783417125529</v>
+        <v>0.2253680141819716</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2047509115476739</v>
+        <v>0.2010946452700368</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1876205824674141</v>
+        <v>0.1895205824674141</v>
       </c>
       <c r="C58">
-        <v>-371.984897161335</v>
+        <v>-388.6729711526608</v>
       </c>
       <c r="D58">
-        <v>314.451102838665</v>
+        <v>310.2940288473393</v>
       </c>
       <c r="E58">
-        <v>166.336</v>
+        <v>178.8670000000001</v>
       </c>
       <c r="F58">
-        <v>701.736</v>
+        <v>714.2670000000001</v>
       </c>
       <c r="G58">
         <v>15.3</v>
@@ -6049,37 +6049,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M58">
-        <v>165.4693488</v>
+        <v>168.4241586</v>
       </c>
       <c r="N58">
-        <v>-132.1943488</v>
+        <v>-135.1491586</v>
       </c>
       <c r="O58">
-        <v>-29.082756736</v>
+        <v>-29.732814892</v>
       </c>
       <c r="P58">
-        <v>-103.111592064</v>
+        <v>-105.416343708</v>
       </c>
       <c r="Q58">
-        <v>-8.011592064000013</v>
+        <v>-10.31634370800002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1395783966488863</v>
+        <v>0.1417592895942092</v>
       </c>
       <c r="T58">
-        <v>2.165782832537791</v>
+        <v>2.216149875154949</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04424082195940812</v>
+        <v>0.04346466718819042</v>
       </c>
       <c r="W58">
-        <v>0.2253680141819716</v>
+        <v>0.2255510314770247</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2010946452700368</v>
+        <v>0.1975666690372292</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1895205824674141</v>
+        <v>0.1914205824674141</v>
       </c>
       <c r="C59">
-        <v>-388.6729711526608</v>
+        <v>-405.2525654160567</v>
       </c>
       <c r="D59">
-        <v>310.2940288473393</v>
+        <v>306.2454345839433</v>
       </c>
       <c r="E59">
-        <v>178.8670000000001</v>
+        <v>191.398</v>
       </c>
       <c r="F59">
-        <v>714.2670000000001</v>
+        <v>726.798</v>
       </c>
       <c r="G59">
         <v>15.3</v>
@@ -6131,37 +6131,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M59">
-        <v>168.4241586</v>
+        <v>171.3789684</v>
       </c>
       <c r="N59">
-        <v>-135.1491586</v>
+        <v>-138.1039684</v>
       </c>
       <c r="O59">
-        <v>-29.732814892</v>
+        <v>-30.382873048</v>
       </c>
       <c r="P59">
-        <v>-105.416343708</v>
+        <v>-107.721095352</v>
       </c>
       <c r="Q59">
-        <v>-10.31634370800002</v>
+        <v>-12.62109535200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1417592895942092</v>
+        <v>0.1440440345845476</v>
       </c>
       <c r="T59">
-        <v>2.216149875154949</v>
+        <v>2.268915348372924</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04346466718819042</v>
+        <v>0.04271527637460094</v>
       </c>
       <c r="W59">
-        <v>0.2255510314770247</v>
+        <v>0.2257277378308691</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1975666690372292</v>
+        <v>0.194160347157277</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1914205824674141</v>
+        <v>0.1933205824674141</v>
       </c>
       <c r="C60">
-        <v>-405.2525654160564</v>
+        <v>-421.7278714645907</v>
       </c>
       <c r="D60">
-        <v>306.2454345839434</v>
+        <v>302.3011285354092</v>
       </c>
       <c r="E60">
-        <v>191.3979999999999</v>
+        <v>203.929</v>
       </c>
       <c r="F60">
-        <v>726.7979999999999</v>
+        <v>739.329</v>
       </c>
       <c r="G60">
         <v>15.3</v>
@@ -6213,37 +6213,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M60">
-        <v>171.3789684</v>
+        <v>174.3337782</v>
       </c>
       <c r="N60">
-        <v>-138.1039684</v>
+        <v>-141.0587782</v>
       </c>
       <c r="O60">
-        <v>-30.382873048</v>
+        <v>-31.032931204</v>
       </c>
       <c r="P60">
-        <v>-107.721095352</v>
+        <v>-110.025846996</v>
       </c>
       <c r="Q60">
-        <v>-12.621095352</v>
+        <v>-14.92584699599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1440440345845476</v>
+        <v>0.1464402305500243</v>
       </c>
       <c r="T60">
-        <v>2.268915348372923</v>
+        <v>2.324254747113726</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04271527637460094</v>
+        <v>0.04199128863943822</v>
       </c>
       <c r="W60">
-        <v>0.2257277378308691</v>
+        <v>0.2258984541388205</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.194160347157277</v>
+        <v>0.1908694938156282</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1933205824674141</v>
+        <v>0.1952205824674141</v>
       </c>
       <c r="C61">
-        <v>-421.7278714645907</v>
+        <v>-438.1028676178149</v>
       </c>
       <c r="D61">
-        <v>302.3011285354092</v>
+        <v>298.457132382185</v>
       </c>
       <c r="E61">
-        <v>203.929</v>
+        <v>216.4599999999999</v>
       </c>
       <c r="F61">
-        <v>739.329</v>
+        <v>751.8599999999999</v>
       </c>
       <c r="G61">
         <v>15.3</v>
@@ -6295,37 +6295,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M61">
-        <v>174.3337782</v>
+        <v>177.288588</v>
       </c>
       <c r="N61">
-        <v>-141.0587782</v>
+        <v>-144.013588</v>
       </c>
       <c r="O61">
-        <v>-31.032931204</v>
+        <v>-31.68298935999999</v>
       </c>
       <c r="P61">
-        <v>-110.025846996</v>
+        <v>-112.33059864</v>
       </c>
       <c r="Q61">
-        <v>-14.92584699599999</v>
+        <v>-17.23059863999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1464402305500243</v>
+        <v>0.1489562363137749</v>
       </c>
       <c r="T61">
-        <v>2.324254747113726</v>
+        <v>2.38236111579157</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04199128863943822</v>
+        <v>0.04129143382878091</v>
       </c>
       <c r="W61">
-        <v>0.2258984541388205</v>
+        <v>0.2260634799031735</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1908694938156282</v>
+        <v>0.1876883355853678</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1952205824674141</v>
+        <v>0.1971205824674141</v>
       </c>
       <c r="C62">
-        <v>-438.1028676178149</v>
+        <v>-454.381332386187</v>
       </c>
       <c r="D62">
-        <v>298.457132382185</v>
+        <v>294.709667613813</v>
       </c>
       <c r="E62">
-        <v>216.4599999999999</v>
+        <v>228.991</v>
       </c>
       <c r="F62">
-        <v>751.8599999999999</v>
+        <v>764.391</v>
       </c>
       <c r="G62">
         <v>15.3</v>
@@ -6377,37 +6377,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M62">
-        <v>177.288588</v>
+        <v>180.2433978</v>
       </c>
       <c r="N62">
-        <v>-144.013588</v>
+        <v>-146.9683978</v>
       </c>
       <c r="O62">
-        <v>-31.68298935999999</v>
+        <v>-32.333047516</v>
       </c>
       <c r="P62">
-        <v>-112.33059864</v>
+        <v>-114.635350284</v>
       </c>
       <c r="Q62">
-        <v>-17.23059863999998</v>
+        <v>-19.535350284</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1489562363137749</v>
+        <v>0.1516012680141281</v>
       </c>
       <c r="T62">
-        <v>2.38236111579157</v>
+        <v>2.443447298247763</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04129143382878091</v>
+        <v>0.04061452507748942</v>
       </c>
       <c r="W62">
-        <v>0.2260634799031735</v>
+        <v>0.226223094986728</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1876883355853678</v>
+        <v>0.1846114776249519</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1971205824674141</v>
+        <v>0.1990205824674141</v>
       </c>
       <c r="C63">
-        <v>-454.381332386187</v>
+        <v>-470.5668568596553</v>
       </c>
       <c r="D63">
-        <v>294.709667613813</v>
+        <v>291.0551431403446</v>
       </c>
       <c r="E63">
-        <v>228.991</v>
+        <v>241.5219999999999</v>
       </c>
       <c r="F63">
-        <v>764.391</v>
+        <v>776.9219999999999</v>
       </c>
       <c r="G63">
         <v>15.3</v>
@@ -6459,37 +6459,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M63">
-        <v>180.2433978</v>
+        <v>183.1982076</v>
       </c>
       <c r="N63">
-        <v>-146.9683978</v>
+        <v>-149.9232076</v>
       </c>
       <c r="O63">
-        <v>-32.333047516</v>
+        <v>-32.98310567199999</v>
       </c>
       <c r="P63">
-        <v>-114.635350284</v>
+        <v>-116.940101928</v>
       </c>
       <c r="Q63">
-        <v>-19.535350284</v>
+        <v>-21.840101928</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1516012680141281</v>
+        <v>0.1543855119092368</v>
       </c>
       <c r="T63">
-        <v>2.443447298247763</v>
+        <v>2.507748542938494</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04061452507748942</v>
+        <v>0.03995945209236863</v>
       </c>
       <c r="W63">
-        <v>0.226223094986728</v>
+        <v>0.2263775611966195</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1846114776249519</v>
+        <v>0.1816338731471301</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1990205824674141</v>
+        <v>0.2009205824674141</v>
       </c>
       <c r="C64">
-        <v>-470.5668568596553</v>
+        <v>-486.6628561857945</v>
       </c>
       <c r="D64">
-        <v>291.0551431403446</v>
+        <v>287.4901438142055</v>
       </c>
       <c r="E64">
-        <v>241.5219999999999</v>
+        <v>254.053</v>
       </c>
       <c r="F64">
-        <v>776.9219999999999</v>
+        <v>789.453</v>
       </c>
       <c r="G64">
         <v>15.3</v>
@@ -6541,37 +6541,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M64">
-        <v>183.1982076</v>
+        <v>186.1530174</v>
       </c>
       <c r="N64">
-        <v>-149.9232076</v>
+        <v>-152.8780174</v>
       </c>
       <c r="O64">
-        <v>-32.98310567199999</v>
+        <v>-33.633163828</v>
       </c>
       <c r="P64">
-        <v>-116.940101928</v>
+        <v>-119.244853572</v>
       </c>
       <c r="Q64">
-        <v>-21.840101928</v>
+        <v>-24.14485357200002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1543855119092368</v>
+        <v>0.1573202554743513</v>
       </c>
       <c r="T64">
-        <v>2.507748542938494</v>
+        <v>2.57552553058548</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03995945209236863</v>
+        <v>0.03932517507502943</v>
       </c>
       <c r="W64">
-        <v>0.2263775611966195</v>
+        <v>0.2265271237173081</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1816338731471301</v>
+        <v>0.1787507957955884</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2009205824674141</v>
+        <v>0.2028205824674141</v>
       </c>
       <c r="C65">
-        <v>-486.6628561857945</v>
+        <v>-502.6725802146036</v>
       </c>
       <c r="D65">
-        <v>287.4901438142055</v>
+        <v>284.0114197853963</v>
       </c>
       <c r="E65">
-        <v>254.053</v>
+        <v>266.5839999999999</v>
       </c>
       <c r="F65">
-        <v>789.453</v>
+        <v>801.9839999999999</v>
       </c>
       <c r="G65">
         <v>15.3</v>
@@ -6623,37 +6623,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M65">
-        <v>186.1530174</v>
+        <v>189.1078272</v>
       </c>
       <c r="N65">
-        <v>-152.8780174</v>
+        <v>-155.8328272</v>
       </c>
       <c r="O65">
-        <v>-33.633163828</v>
+        <v>-34.283221984</v>
       </c>
       <c r="P65">
-        <v>-119.244853572</v>
+        <v>-121.549605216</v>
       </c>
       <c r="Q65">
-        <v>-24.14485357200002</v>
+        <v>-26.44960521600001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1573202554743513</v>
+        <v>0.1604180403486388</v>
       </c>
       <c r="T65">
-        <v>2.57552553058548</v>
+        <v>2.647067906435077</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03932517507502943</v>
+        <v>0.0387107192144821</v>
       </c>
       <c r="W65">
-        <v>0.2265271237173081</v>
+        <v>0.2266720124092251</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1787507957955884</v>
+        <v>0.1759578146112822</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2028205824674141</v>
+        <v>0.2047205824674141</v>
       </c>
       <c r="C66">
-        <v>-502.6725802146036</v>
+        <v>-518.599123379712</v>
       </c>
       <c r="D66">
-        <v>284.0114197853963</v>
+        <v>280.6158766202881</v>
       </c>
       <c r="E66">
-        <v>266.5839999999999</v>
+        <v>279.115</v>
       </c>
       <c r="F66">
-        <v>801.9839999999999</v>
+        <v>814.515</v>
       </c>
       <c r="G66">
         <v>15.3</v>
@@ -6705,37 +6705,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M66">
-        <v>189.1078272</v>
+        <v>192.062637</v>
       </c>
       <c r="N66">
-        <v>-155.8328272</v>
+        <v>-158.787637</v>
       </c>
       <c r="O66">
-        <v>-34.283221984</v>
+        <v>-34.93328014</v>
       </c>
       <c r="P66">
-        <v>-121.549605216</v>
+        <v>-123.85435686</v>
       </c>
       <c r="Q66">
-        <v>-26.44960521600001</v>
+        <v>-28.75435686</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1604180403486388</v>
+        <v>0.1636928415014571</v>
       </c>
       <c r="T66">
-        <v>2.647067906435077</v>
+        <v>2.722698418047508</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0387107192144821</v>
+        <v>0.03811516968810546</v>
       </c>
       <c r="W66">
-        <v>0.2266720124092251</v>
+        <v>0.2268124429875447</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1759578146112822</v>
+        <v>0.1732507713095702</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2047205824674141</v>
+        <v>0.206620582467414</v>
       </c>
       <c r="C67">
-        <v>-518.599123379712</v>
+        <v>-534.4454338791411</v>
       </c>
       <c r="D67">
-        <v>280.6158766202881</v>
+        <v>277.3005661208589</v>
       </c>
       <c r="E67">
-        <v>279.115</v>
+        <v>291.646</v>
       </c>
       <c r="F67">
-        <v>814.515</v>
+        <v>827.0459999999999</v>
       </c>
       <c r="G67">
         <v>15.3</v>
@@ -6787,37 +6787,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M67">
-        <v>192.062637</v>
+        <v>195.0174468</v>
       </c>
       <c r="N67">
-        <v>-158.787637</v>
+        <v>-161.7424468</v>
       </c>
       <c r="O67">
-        <v>-34.93328014</v>
+        <v>-35.58333829599999</v>
       </c>
       <c r="P67">
-        <v>-123.85435686</v>
+        <v>-126.159108504</v>
       </c>
       <c r="Q67">
-        <v>-28.75435686</v>
+        <v>-31.05910850399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1636928415014571</v>
+        <v>0.1671602780162058</v>
       </c>
       <c r="T67">
-        <v>2.722698418047508</v>
+        <v>2.8027777832842</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03811516968810546</v>
+        <v>0.03753766711707356</v>
       </c>
       <c r="W67">
-        <v>0.2268124429875447</v>
+        <v>0.2269486180937941</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1732507713095702</v>
+        <v>0.1706257596230616</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.206620582467414</v>
+        <v>0.2085205824674141</v>
       </c>
       <c r="C68">
-        <v>-534.4454338791411</v>
+        <v>-550.2143222128752</v>
       </c>
       <c r="D68">
-        <v>277.3005661208589</v>
+        <v>274.0626777871248</v>
       </c>
       <c r="E68">
-        <v>291.646</v>
+        <v>304.177</v>
       </c>
       <c r="F68">
-        <v>827.0459999999999</v>
+        <v>839.577</v>
       </c>
       <c r="G68">
         <v>15.3</v>
@@ -6869,37 +6869,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M68">
-        <v>195.0174468</v>
+        <v>197.9722566</v>
       </c>
       <c r="N68">
-        <v>-161.7424468</v>
+        <v>-164.6972566</v>
       </c>
       <c r="O68">
-        <v>-35.58333829599999</v>
+        <v>-36.233396452</v>
       </c>
       <c r="P68">
-        <v>-126.159108504</v>
+        <v>-128.463860148</v>
       </c>
       <c r="Q68">
-        <v>-31.05910850399999</v>
+        <v>-33.36386014800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1671602780162058</v>
+        <v>0.1708378621985151</v>
       </c>
       <c r="T68">
-        <v>2.8027777832842</v>
+        <v>2.887710443383721</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03753766711707356</v>
+        <v>0.03697740342875903</v>
       </c>
       <c r="W68">
-        <v>0.2269486180937941</v>
+        <v>0.2270807282714986</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1706257596230616</v>
+        <v>0.1680791064943592</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2085205824674141</v>
+        <v>0.2104205824674141</v>
       </c>
       <c r="C69">
-        <v>-550.2143222128752</v>
+        <v>-565.9084691292009</v>
       </c>
       <c r="D69">
-        <v>274.0626777871248</v>
+        <v>270.8995308707991</v>
       </c>
       <c r="E69">
-        <v>304.177</v>
+        <v>316.708</v>
       </c>
       <c r="F69">
-        <v>839.577</v>
+        <v>852.1079999999999</v>
       </c>
       <c r="G69">
         <v>15.3</v>
@@ -6951,37 +6951,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M69">
-        <v>197.9722566</v>
+        <v>200.9270664</v>
       </c>
       <c r="N69">
-        <v>-164.6972566</v>
+        <v>-167.6520664</v>
       </c>
       <c r="O69">
-        <v>-36.233396452</v>
+        <v>-36.883454608</v>
       </c>
       <c r="P69">
-        <v>-128.463860148</v>
+        <v>-130.768611792</v>
       </c>
       <c r="Q69">
-        <v>-33.36386014800001</v>
+        <v>-35.66861179200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1708378621985151</v>
+        <v>0.1747452953922187</v>
       </c>
       <c r="T69">
-        <v>2.887710443383721</v>
+        <v>2.977951394739462</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03697740342875903</v>
+        <v>0.03643361808421845</v>
       </c>
       <c r="W69">
-        <v>0.2270807282714986</v>
+        <v>0.2272089528557413</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1680791064943592</v>
+        <v>0.1656073549282657</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2104205824674141</v>
+        <v>0.2123205824674141</v>
       </c>
       <c r="C70">
-        <v>-565.9084691292009</v>
+        <v>-581.5304330270435</v>
       </c>
       <c r="D70">
-        <v>270.8995308707991</v>
+        <v>267.8085669729566</v>
       </c>
       <c r="E70">
-        <v>316.708</v>
+        <v>329.239</v>
       </c>
       <c r="F70">
-        <v>852.1079999999999</v>
+        <v>864.639</v>
       </c>
       <c r="G70">
         <v>15.3</v>
@@ -7033,37 +7033,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M70">
-        <v>200.9270664</v>
+        <v>203.8818762</v>
       </c>
       <c r="N70">
-        <v>-167.6520664</v>
+        <v>-170.6068762</v>
       </c>
       <c r="O70">
-        <v>-36.883454608</v>
+        <v>-37.533512764</v>
       </c>
       <c r="P70">
-        <v>-130.768611792</v>
+        <v>-133.073363436</v>
       </c>
       <c r="Q70">
-        <v>-35.66861179200001</v>
+        <v>-37.97336343600003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1747452953922187</v>
+        <v>0.1789048210500322</v>
       </c>
       <c r="T70">
-        <v>2.977951394739462</v>
+        <v>3.074014342956864</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03643361808421845</v>
+        <v>0.03590559463372252</v>
       </c>
       <c r="W70">
-        <v>0.2272089528557413</v>
+        <v>0.2273334607853682</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1656073549282657</v>
+        <v>0.1632072483351024</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2123205824674141</v>
+        <v>0.2142205824674141</v>
       </c>
       <c r="C71">
-        <v>-581.5304330270435</v>
+        <v>-597.0826568572548</v>
       </c>
       <c r="D71">
-        <v>267.8085669729566</v>
+        <v>264.7873431427452</v>
       </c>
       <c r="E71">
-        <v>329.239</v>
+        <v>341.7700000000001</v>
       </c>
       <c r="F71">
-        <v>864.639</v>
+        <v>877.1700000000001</v>
       </c>
       <c r="G71">
         <v>15.3</v>
@@ -7115,37 +7115,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M71">
-        <v>203.8818762</v>
+        <v>206.836686</v>
       </c>
       <c r="N71">
-        <v>-170.6068762</v>
+        <v>-173.561686</v>
       </c>
       <c r="O71">
-        <v>-37.533512764</v>
+        <v>-38.18357092</v>
       </c>
       <c r="P71">
-        <v>-133.073363436</v>
+        <v>-135.37811508</v>
       </c>
       <c r="Q71">
-        <v>-37.97336343600003</v>
+        <v>-40.27811508000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1789048210500322</v>
+        <v>0.1833416484183666</v>
       </c>
       <c r="T71">
-        <v>3.074014342956864</v>
+        <v>3.176481487722093</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03590559463372252</v>
+        <v>0.03539265756752649</v>
       </c>
       <c r="W71">
-        <v>0.2273334607853682</v>
+        <v>0.2274544113455773</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1632072483351024</v>
+        <v>0.1608757162160295</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2142205824674141</v>
+        <v>0.2161205824674141</v>
       </c>
       <c r="C72">
-        <v>-597.0826568572548</v>
+        <v>-612.5674745619792</v>
       </c>
       <c r="D72">
-        <v>264.7873431427452</v>
+        <v>261.8335254380207</v>
       </c>
       <c r="E72">
-        <v>341.7700000000001</v>
+        <v>354.301</v>
       </c>
       <c r="F72">
-        <v>877.1700000000001</v>
+        <v>889.701</v>
       </c>
       <c r="G72">
         <v>15.3</v>
@@ -7197,37 +7197,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M72">
-        <v>206.836686</v>
+        <v>209.7914958</v>
       </c>
       <c r="N72">
-        <v>-173.561686</v>
+        <v>-176.5164958</v>
       </c>
       <c r="O72">
-        <v>-38.18357092</v>
+        <v>-38.833629076</v>
       </c>
       <c r="P72">
-        <v>-135.37811508</v>
+        <v>-137.682866724</v>
       </c>
       <c r="Q72">
-        <v>-40.27811508000002</v>
+        <v>-42.58286672400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1833416484183666</v>
+        <v>0.1880844638810689</v>
       </c>
       <c r="T72">
-        <v>3.176481487722093</v>
+        <v>3.286015332126304</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03539265756752649</v>
+        <v>0.0348941694327726</v>
       </c>
       <c r="W72">
-        <v>0.2274544113455773</v>
+        <v>0.2275719548477523</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1608757162160295</v>
+        <v>0.1586098610580573</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2161205824674141</v>
+        <v>0.2180205824674141</v>
       </c>
       <c r="C73">
-        <v>-612.567474561979</v>
+        <v>-627.9871170877723</v>
       </c>
       <c r="D73">
-        <v>261.8335254380208</v>
+        <v>258.9448829122275</v>
       </c>
       <c r="E73">
-        <v>354.3009999999999</v>
+        <v>366.8319999999999</v>
       </c>
       <c r="F73">
-        <v>889.7009999999999</v>
+        <v>902.2319999999999</v>
       </c>
       <c r="G73">
         <v>15.3</v>
@@ -7279,37 +7279,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M73">
-        <v>209.7914958</v>
+        <v>212.7463056</v>
       </c>
       <c r="N73">
-        <v>-176.5164958</v>
+        <v>-179.4713056</v>
       </c>
       <c r="O73">
-        <v>-38.83362907599999</v>
+        <v>-39.48368723199999</v>
       </c>
       <c r="P73">
-        <v>-137.682866724</v>
+        <v>-139.987618368</v>
       </c>
       <c r="Q73">
-        <v>-42.58286672399998</v>
+        <v>-44.88761836799998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1880844638810689</v>
+        <v>0.1931660518768213</v>
       </c>
       <c r="T73">
-        <v>3.286015332126303</v>
+        <v>3.403373022559385</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03489416943277261</v>
+        <v>0.03440952819065076</v>
       </c>
       <c r="W73">
-        <v>0.2275719548477523</v>
+        <v>0.2276862332526446</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1586098610580573</v>
+        <v>0.1564069463211398</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2180205824674141</v>
+        <v>0.2199205824674141</v>
       </c>
       <c r="C74">
-        <v>-627.9871170877723</v>
+        <v>-643.3437180050294</v>
       </c>
       <c r="D74">
-        <v>258.9448829122275</v>
+        <v>256.1192819949705</v>
       </c>
       <c r="E74">
-        <v>366.8319999999999</v>
+        <v>379.3629999999999</v>
       </c>
       <c r="F74">
-        <v>902.2319999999999</v>
+        <v>914.7629999999999</v>
       </c>
       <c r="G74">
         <v>15.3</v>
@@ -7361,37 +7361,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M74">
-        <v>212.7463056</v>
+        <v>215.7011154</v>
       </c>
       <c r="N74">
-        <v>-179.4713056</v>
+        <v>-182.4261154</v>
       </c>
       <c r="O74">
-        <v>-39.48368723199999</v>
+        <v>-40.13374538799999</v>
       </c>
       <c r="P74">
-        <v>-139.987618368</v>
+        <v>-142.292370012</v>
       </c>
       <c r="Q74">
-        <v>-44.88761836799998</v>
+        <v>-47.192370012</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1931660518768213</v>
+        <v>0.1986240537981851</v>
       </c>
       <c r="T74">
-        <v>3.403373022559385</v>
+        <v>3.529423875246769</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03440952819065076</v>
+        <v>0.03393816479077883</v>
       </c>
       <c r="W74">
-        <v>0.2276862332526446</v>
+        <v>0.2277973807423344</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1564069463211398</v>
+        <v>0.1542643854126311</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2199205824674141</v>
+        <v>0.2218205824674141</v>
       </c>
       <c r="C75">
-        <v>-643.3437180050294</v>
+        <v>-658.639318763469</v>
       </c>
       <c r="D75">
-        <v>256.1192819949705</v>
+        <v>253.354681236531</v>
       </c>
       <c r="E75">
-        <v>379.3629999999999</v>
+        <v>391.8939999999999</v>
       </c>
       <c r="F75">
-        <v>914.7629999999999</v>
+        <v>927.2939999999999</v>
       </c>
       <c r="G75">
         <v>15.3</v>
@@ -7443,37 +7443,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M75">
-        <v>215.7011154</v>
+        <v>218.6559252</v>
       </c>
       <c r="N75">
-        <v>-182.4261154</v>
+        <v>-185.3809252</v>
       </c>
       <c r="O75">
-        <v>-40.13374538799999</v>
+        <v>-40.78380354399999</v>
       </c>
       <c r="P75">
-        <v>-142.292370012</v>
+        <v>-144.597121656</v>
       </c>
       <c r="Q75">
-        <v>-47.192370012</v>
+        <v>-49.49712165599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1986240537981851</v>
+        <v>0.2045019020211922</v>
       </c>
       <c r="T75">
-        <v>3.529423875246769</v>
+        <v>3.665170947371645</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03393816479077883</v>
+        <v>0.0334795409422548</v>
       </c>
       <c r="W75">
-        <v>0.2277973807423344</v>
+        <v>0.2279055242458163</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1542643854126311</v>
+        <v>0.1521797315557036</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2218205824674141</v>
+        <v>0.2237205824674141</v>
       </c>
       <c r="C76">
-        <v>-658.639318763469</v>
+        <v>-673.875873610883</v>
       </c>
       <c r="D76">
-        <v>253.354681236531</v>
+        <v>250.6491263891169</v>
       </c>
       <c r="E76">
-        <v>391.8939999999999</v>
+        <v>404.425</v>
       </c>
       <c r="F76">
-        <v>927.2939999999999</v>
+        <v>939.8249999999999</v>
       </c>
       <c r="G76">
         <v>15.3</v>
@@ -7525,37 +7525,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M76">
-        <v>218.6559252</v>
+        <v>221.610735</v>
       </c>
       <c r="N76">
-        <v>-185.3809252</v>
+        <v>-188.335735</v>
       </c>
       <c r="O76">
-        <v>-40.78380354399999</v>
+        <v>-41.4338617</v>
       </c>
       <c r="P76">
-        <v>-144.597121656</v>
+        <v>-146.9018733</v>
       </c>
       <c r="Q76">
-        <v>-49.49712165599999</v>
+        <v>-51.80187330000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2045019020211922</v>
+        <v>0.2108499781020399</v>
       </c>
       <c r="T76">
-        <v>3.665170947371645</v>
+        <v>3.811777785266511</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0334795409422548</v>
+        <v>0.03303314706302473</v>
       </c>
       <c r="W76">
-        <v>0.2279055242458163</v>
+        <v>0.2280107839225388</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1521797315557036</v>
+        <v>0.1501506684682942</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2237205824674141</v>
+        <v>0.225620582467414</v>
       </c>
       <c r="C77">
-        <v>-673.875873610883</v>
+        <v>-689.0552542000494</v>
       </c>
       <c r="D77">
-        <v>250.6491263891169</v>
+        <v>248.0007457999507</v>
       </c>
       <c r="E77">
-        <v>404.425</v>
+        <v>416.956</v>
       </c>
       <c r="F77">
-        <v>939.8249999999999</v>
+        <v>952.356</v>
       </c>
       <c r="G77">
         <v>15.3</v>
@@ -7607,37 +7607,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M77">
-        <v>221.610735</v>
+        <v>224.5655448</v>
       </c>
       <c r="N77">
-        <v>-188.335735</v>
+        <v>-191.2905448</v>
       </c>
       <c r="O77">
-        <v>-41.4338617</v>
+        <v>-42.083919856</v>
       </c>
       <c r="P77">
-        <v>-146.9018733</v>
+        <v>-149.206624944</v>
       </c>
       <c r="Q77">
-        <v>-51.80187330000001</v>
+        <v>-54.106624944</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2108499781020399</v>
+        <v>0.2177270605229583</v>
       </c>
       <c r="T77">
-        <v>3.811777785266511</v>
+        <v>3.970601859652616</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03303314706302473</v>
+        <v>0.03259850039114282</v>
       </c>
       <c r="W77">
-        <v>0.2280107839225388</v>
+        <v>0.2281132736077685</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1501506684682942</v>
+        <v>0.148175001777922</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.225620582467414</v>
+        <v>0.2275205824674141</v>
       </c>
       <c r="C78">
-        <v>-689.0552542000494</v>
+        <v>-704.1792539066423</v>
       </c>
       <c r="D78">
-        <v>248.0007457999507</v>
+        <v>245.4077460933577</v>
       </c>
       <c r="E78">
-        <v>416.956</v>
+        <v>429.487</v>
       </c>
       <c r="F78">
-        <v>952.356</v>
+        <v>964.8869999999999</v>
       </c>
       <c r="G78">
         <v>15.3</v>
@@ -7689,37 +7689,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M78">
-        <v>224.5655448</v>
+        <v>227.5203546</v>
       </c>
       <c r="N78">
-        <v>-191.2905448</v>
+        <v>-194.2453546</v>
       </c>
       <c r="O78">
-        <v>-42.083919856</v>
+        <v>-42.73397801199999</v>
       </c>
       <c r="P78">
-        <v>-149.206624944</v>
+        <v>-151.511376588</v>
       </c>
       <c r="Q78">
-        <v>-54.106624944</v>
+        <v>-56.411376588</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2177270605229583</v>
+        <v>0.225202150110913</v>
       </c>
       <c r="T78">
-        <v>3.970601859652616</v>
+        <v>4.143236723115773</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03259850039114282</v>
+        <v>0.0321751432432059</v>
       </c>
       <c r="W78">
-        <v>0.2281132736077685</v>
+        <v>0.2282131012232521</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.148175001777922</v>
+        <v>0.1462506511054814</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2275205824674141</v>
+        <v>0.2294205824674141</v>
       </c>
       <c r="C79">
-        <v>-704.1792539066423</v>
+        <v>-719.2495918790623</v>
       </c>
       <c r="D79">
-        <v>245.4077460933577</v>
+        <v>242.8684081209376</v>
       </c>
       <c r="E79">
-        <v>429.487</v>
+        <v>442.018</v>
       </c>
       <c r="F79">
-        <v>964.8869999999999</v>
+        <v>977.418</v>
       </c>
       <c r="G79">
         <v>15.3</v>
@@ -7771,37 +7771,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M79">
-        <v>227.5203546</v>
+        <v>230.4751644</v>
       </c>
       <c r="N79">
-        <v>-194.2453546</v>
+        <v>-197.2001644</v>
       </c>
       <c r="O79">
-        <v>-42.73397801199999</v>
+        <v>-43.384036168</v>
       </c>
       <c r="P79">
-        <v>-151.511376588</v>
+        <v>-153.816128232</v>
       </c>
       <c r="Q79">
-        <v>-56.411376588</v>
+        <v>-58.71612823200002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.225202150110913</v>
+        <v>0.2333567932977726</v>
       </c>
       <c r="T79">
-        <v>4.143236723115773</v>
+        <v>4.331565665075582</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0321751432432059</v>
+        <v>0.03176264140675455</v>
       </c>
       <c r="W79">
-        <v>0.2282131012232521</v>
+        <v>0.2283103691562873</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1462506511054814</v>
+        <v>0.1443756427579752</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2294205824674141</v>
+        <v>0.2313205824674141</v>
       </c>
       <c r="C80">
-        <v>-719.2495918790623</v>
+        <v>-734.267916839412</v>
       </c>
       <c r="D80">
-        <v>242.8684081209376</v>
+        <v>240.3810831605879</v>
       </c>
       <c r="E80">
-        <v>442.018</v>
+        <v>454.549</v>
       </c>
       <c r="F80">
-        <v>977.418</v>
+        <v>989.949</v>
       </c>
       <c r="G80">
         <v>15.3</v>
@@ -7853,37 +7853,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M80">
-        <v>230.4751644</v>
+        <v>233.4299742</v>
       </c>
       <c r="N80">
-        <v>-197.2001644</v>
+        <v>-200.1549742</v>
       </c>
       <c r="O80">
-        <v>-43.384036168</v>
+        <v>-44.034094324</v>
       </c>
       <c r="P80">
-        <v>-153.816128232</v>
+        <v>-156.120879876</v>
       </c>
       <c r="Q80">
-        <v>-58.71612823200002</v>
+        <v>-61.02087987600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2333567932977726</v>
+        <v>0.2422880691690952</v>
       </c>
       <c r="T80">
-        <v>4.331565665075582</v>
+        <v>4.537830696745848</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03176264140675455</v>
+        <v>0.03136058265477031</v>
       </c>
       <c r="W80">
-        <v>0.2283103691562873</v>
+        <v>0.2284051746100052</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1443756427579752</v>
+        <v>0.1425481029762287</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2313205824674141</v>
+        <v>0.2332205824674141</v>
       </c>
       <c r="C81">
-        <v>-734.267916839412</v>
+        <v>-749.2358106532733</v>
       </c>
       <c r="D81">
-        <v>240.3810831605879</v>
+        <v>237.9441893467267</v>
       </c>
       <c r="E81">
-        <v>454.549</v>
+        <v>467.08</v>
       </c>
       <c r="F81">
-        <v>989.949</v>
+        <v>1002.48</v>
       </c>
       <c r="G81">
         <v>15.3</v>
@@ -7935,37 +7935,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M81">
-        <v>233.4299742</v>
+        <v>236.384784</v>
       </c>
       <c r="N81">
-        <v>-200.1549742</v>
+        <v>-203.109784</v>
       </c>
       <c r="O81">
-        <v>-44.034094324</v>
+        <v>-44.68415248</v>
       </c>
       <c r="P81">
-        <v>-156.120879876</v>
+        <v>-158.42563152</v>
       </c>
       <c r="Q81">
-        <v>-61.02087987600001</v>
+        <v>-63.32563152000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2422880691690952</v>
+        <v>0.2521124726275499</v>
       </c>
       <c r="T81">
-        <v>4.537830696745848</v>
+        <v>4.764722231583139</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03136058265477031</v>
+        <v>0.03096857537158568</v>
       </c>
       <c r="W81">
-        <v>0.2284051746100052</v>
+        <v>0.2284976099273801</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1425481029762287</v>
+        <v>0.1407662516890258</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2332205824674141</v>
+        <v>0.2351205824674141</v>
       </c>
       <c r="C82">
-        <v>-749.2358106532733</v>
+        <v>-764.1547916845307</v>
       </c>
       <c r="D82">
-        <v>237.9441893467267</v>
+        <v>235.5562083154693</v>
       </c>
       <c r="E82">
-        <v>467.08</v>
+        <v>479.611</v>
       </c>
       <c r="F82">
-        <v>1002.48</v>
+        <v>1015.011</v>
       </c>
       <c r="G82">
         <v>15.3</v>
@@ -8017,37 +8017,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M82">
-        <v>236.384784</v>
+        <v>239.3395938</v>
       </c>
       <c r="N82">
-        <v>-203.109784</v>
+        <v>-206.0645938</v>
       </c>
       <c r="O82">
-        <v>-44.68415248</v>
+        <v>-45.33421063599999</v>
       </c>
       <c r="P82">
-        <v>-158.42563152</v>
+        <v>-160.730383164</v>
       </c>
       <c r="Q82">
-        <v>-63.32563152000003</v>
+        <v>-65.63038316399999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2521124726275499</v>
+        <v>0.2629710238184736</v>
       </c>
       <c r="T82">
-        <v>4.764722231583139</v>
+        <v>5.015497085876989</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03096857537158568</v>
+        <v>0.03058624728057845</v>
       </c>
       <c r="W82">
-        <v>0.2284976099273801</v>
+        <v>0.2285877628912396</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1407662516890258</v>
+        <v>0.1390283967299021</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2351205824674141</v>
+        <v>0.2370205824674141</v>
       </c>
       <c r="C83">
-        <v>-764.1547916845307</v>
+        <v>-779.0263179501886</v>
       </c>
       <c r="D83">
-        <v>235.5562083154693</v>
+        <v>233.2156820498112</v>
       </c>
       <c r="E83">
-        <v>479.611</v>
+        <v>492.1419999999999</v>
       </c>
       <c r="F83">
-        <v>1015.011</v>
+        <v>1027.542</v>
       </c>
       <c r="G83">
         <v>15.3</v>
@@ -8099,37 +8099,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M83">
-        <v>239.3395938</v>
+        <v>242.2944036</v>
       </c>
       <c r="N83">
-        <v>-206.0645938</v>
+        <v>-209.0194036</v>
       </c>
       <c r="O83">
-        <v>-45.33421063599999</v>
+        <v>-45.98426879199999</v>
       </c>
       <c r="P83">
-        <v>-160.730383164</v>
+        <v>-163.035134808</v>
       </c>
       <c r="Q83">
-        <v>-65.63038316399999</v>
+        <v>-67.93513480799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2629710238184736</v>
+        <v>0.2750360806972777</v>
       </c>
       <c r="T83">
-        <v>5.015497085876989</v>
+        <v>5.294135812870156</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03058624728057845</v>
+        <v>0.03021324426496164</v>
       </c>
       <c r="W83">
-        <v>0.2285877628912396</v>
+        <v>0.2286757170023221</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1390283967299021</v>
+        <v>0.1373329284770983</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2370205824674141</v>
+        <v>0.2389205824674141</v>
       </c>
       <c r="C84">
-        <v>-779.0263179501886</v>
+        <v>-793.8517900889593</v>
       </c>
       <c r="D84">
-        <v>233.2156820498112</v>
+        <v>230.9212099110408</v>
       </c>
       <c r="E84">
-        <v>492.1419999999999</v>
+        <v>504.6730000000001</v>
       </c>
       <c r="F84">
-        <v>1027.542</v>
+        <v>1040.073</v>
       </c>
       <c r="G84">
         <v>15.3</v>
@@ -8181,37 +8181,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M84">
-        <v>242.2944036</v>
+        <v>245.2492134</v>
       </c>
       <c r="N84">
-        <v>-209.0194036</v>
+        <v>-211.9742134</v>
       </c>
       <c r="O84">
-        <v>-45.98426879199999</v>
+        <v>-46.63432694800001</v>
       </c>
       <c r="P84">
-        <v>-163.035134808</v>
+        <v>-165.339886452</v>
       </c>
       <c r="Q84">
-        <v>-67.93513480799999</v>
+        <v>-70.23988645200004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2750360806972777</v>
+        <v>0.2885205560324117</v>
       </c>
       <c r="T84">
-        <v>5.294135812870156</v>
+        <v>5.605555566568401</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03021324426496164</v>
+        <v>0.02984922927381752</v>
       </c>
       <c r="W84">
-        <v>0.2286757170023221</v>
+        <v>0.2287615517372338</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1373329284770983</v>
+        <v>0.1356783148809887</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2389205824674141</v>
+        <v>0.2408205824674141</v>
       </c>
       <c r="C85">
-        <v>-793.8517900889593</v>
+        <v>-808.6325541563201</v>
       </c>
       <c r="D85">
-        <v>230.9212099110408</v>
+        <v>228.6714458436799</v>
       </c>
       <c r="E85">
-        <v>504.6730000000001</v>
+        <v>517.2040000000001</v>
       </c>
       <c r="F85">
-        <v>1040.073</v>
+        <v>1052.604</v>
       </c>
       <c r="G85">
         <v>15.3</v>
@@ -8263,37 +8263,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M85">
-        <v>245.2492134</v>
+        <v>248.2040232</v>
       </c>
       <c r="N85">
-        <v>-211.9742134</v>
+        <v>-214.9290232</v>
       </c>
       <c r="O85">
-        <v>-46.63432694800001</v>
+        <v>-47.284385104</v>
       </c>
       <c r="P85">
-        <v>-165.339886452</v>
+        <v>-167.644638096</v>
       </c>
       <c r="Q85">
-        <v>-70.23988645200004</v>
+        <v>-72.54463809600003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2885205560324117</v>
+        <v>0.3036905907844375</v>
       </c>
       <c r="T85">
-        <v>5.605555566568401</v>
+        <v>5.955902789478927</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02984922927381752</v>
+        <v>0.02949388130627208</v>
       </c>
       <c r="W85">
-        <v>0.2287615517372338</v>
+        <v>0.228845342787981</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1356783148809887</v>
+        <v>0.1340630968466913</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2408205824674141</v>
+        <v>0.2427205824674141</v>
       </c>
       <c r="C86">
-        <v>-808.63255415632</v>
+        <v>-823.3699042577622</v>
       </c>
       <c r="D86">
-        <v>228.6714458436798</v>
+        <v>226.4650957422378</v>
       </c>
       <c r="E86">
-        <v>517.2039999999998</v>
+        <v>529.735</v>
       </c>
       <c r="F86">
-        <v>1052.604</v>
+        <v>1065.135</v>
       </c>
       <c r="G86">
         <v>15.3</v>
@@ -8345,37 +8345,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M86">
-        <v>248.2040232</v>
+        <v>251.158833</v>
       </c>
       <c r="N86">
-        <v>-214.9290232</v>
+        <v>-217.883833</v>
       </c>
       <c r="O86">
-        <v>-47.28438510399999</v>
+        <v>-47.93444326</v>
       </c>
       <c r="P86">
-        <v>-167.644638096</v>
+        <v>-169.94938974</v>
       </c>
       <c r="Q86">
-        <v>-72.54463809599997</v>
+        <v>-74.84938974000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3036905907844373</v>
+        <v>0.3208832968367332</v>
       </c>
       <c r="T86">
-        <v>5.955902789478923</v>
+        <v>6.352962975444185</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02949388130627208</v>
+        <v>0.02914689446737476</v>
       </c>
       <c r="W86">
-        <v>0.228845342787981</v>
+        <v>0.2289271622845931</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1340630968466913</v>
+        <v>0.1324858839426125</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2427205824674141</v>
+        <v>0.2446205824674141</v>
       </c>
       <c r="C87">
-        <v>-823.3699042577622</v>
+        <v>-838.0650850310517</v>
       </c>
       <c r="D87">
-        <v>226.4650957422378</v>
+        <v>224.3009149689483</v>
       </c>
       <c r="E87">
-        <v>529.735</v>
+        <v>542.266</v>
       </c>
       <c r="F87">
-        <v>1065.135</v>
+        <v>1077.666</v>
       </c>
       <c r="G87">
         <v>15.3</v>
@@ -8427,37 +8427,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M87">
-        <v>251.158833</v>
+        <v>254.1136428</v>
       </c>
       <c r="N87">
-        <v>-217.883833</v>
+        <v>-220.8386428</v>
       </c>
       <c r="O87">
-        <v>-47.93444326</v>
+        <v>-48.584501416</v>
       </c>
       <c r="P87">
-        <v>-169.94938974</v>
+        <v>-172.254141384</v>
       </c>
       <c r="Q87">
-        <v>-74.84938974000002</v>
+        <v>-77.15414138400001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3208832968367332</v>
+        <v>0.3405321037536427</v>
       </c>
       <c r="T87">
-        <v>6.352962975444185</v>
+        <v>6.80674604511877</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02914689446737476</v>
+        <v>0.02880797708984715</v>
       </c>
       <c r="W87">
-        <v>0.2289271622845931</v>
+        <v>0.229007079002214</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1324858839426125</v>
+        <v>0.1309453504083962</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2446205824674141</v>
+        <v>0.246520582467414</v>
       </c>
       <c r="C88">
-        <v>-838.0650850310517</v>
+        <v>-852.7192939875133</v>
       </c>
       <c r="D88">
-        <v>224.3009149689483</v>
+        <v>222.1777060124865</v>
       </c>
       <c r="E88">
-        <v>542.266</v>
+        <v>554.7969999999999</v>
       </c>
       <c r="F88">
-        <v>1077.666</v>
+        <v>1090.197</v>
       </c>
       <c r="G88">
         <v>15.3</v>
@@ -8509,37 +8509,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M88">
-        <v>254.1136428</v>
+        <v>257.0684526</v>
       </c>
       <c r="N88">
-        <v>-220.8386428</v>
+        <v>-223.7934526</v>
       </c>
       <c r="O88">
-        <v>-48.584501416</v>
+        <v>-49.234559572</v>
       </c>
       <c r="P88">
-        <v>-172.254141384</v>
+        <v>-174.558893028</v>
       </c>
       <c r="Q88">
-        <v>-77.15414138400001</v>
+        <v>-79.45889302800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3405321037536427</v>
+        <v>0.3632038040423844</v>
       </c>
       <c r="T88">
-        <v>6.80674604511877</v>
+        <v>7.33034189474329</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02880797708984715</v>
+        <v>0.02847685091640063</v>
       </c>
       <c r="W88">
-        <v>0.229007079002214</v>
+        <v>0.2290851585539127</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1309453504083962</v>
+        <v>0.1294402314381846</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.246520582467414</v>
+        <v>0.2484205824674141</v>
       </c>
       <c r="C89">
-        <v>-852.7192939875133</v>
+        <v>-867.3336837215824</v>
       </c>
       <c r="D89">
-        <v>222.1777060124865</v>
+        <v>220.0943162784175</v>
       </c>
       <c r="E89">
-        <v>554.7969999999999</v>
+        <v>567.3279999999999</v>
       </c>
       <c r="F89">
-        <v>1090.197</v>
+        <v>1102.728</v>
       </c>
       <c r="G89">
         <v>15.3</v>
@@ -8591,37 +8591,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M89">
-        <v>257.0684526</v>
+        <v>260.0232624</v>
       </c>
       <c r="N89">
-        <v>-223.7934526</v>
+        <v>-226.7482624</v>
       </c>
       <c r="O89">
-        <v>-49.234559572</v>
+        <v>-49.88461772799999</v>
       </c>
       <c r="P89">
-        <v>-174.558893028</v>
+        <v>-176.863644672</v>
       </c>
       <c r="Q89">
-        <v>-79.45889302800001</v>
+        <v>-81.76364467199997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3632038040423844</v>
+        <v>0.3896541210459165</v>
       </c>
       <c r="T89">
-        <v>7.33034189474329</v>
+        <v>7.941203719305232</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02847685091640063</v>
+        <v>0.02815325033780517</v>
       </c>
       <c r="W89">
-        <v>0.2290851585539127</v>
+        <v>0.2291614635703456</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1294402314381846</v>
+        <v>0.1279693197172962</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2484205824674141</v>
+        <v>0.2503205824674141</v>
       </c>
       <c r="C90">
-        <v>-867.3336837215824</v>
+        <v>-881.9093639972004</v>
       </c>
       <c r="D90">
-        <v>220.0943162784175</v>
+        <v>218.0496360027995</v>
       </c>
       <c r="E90">
-        <v>567.3279999999999</v>
+        <v>579.859</v>
       </c>
       <c r="F90">
-        <v>1102.728</v>
+        <v>1115.259</v>
       </c>
       <c r="G90">
         <v>15.3</v>
@@ -8673,37 +8673,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M90">
-        <v>260.0232624</v>
+        <v>262.9780722</v>
       </c>
       <c r="N90">
-        <v>-226.7482624</v>
+        <v>-229.7030722</v>
       </c>
       <c r="O90">
-        <v>-49.88461772799999</v>
+        <v>-50.53467588400001</v>
       </c>
       <c r="P90">
-        <v>-176.863644672</v>
+        <v>-179.168396316</v>
       </c>
       <c r="Q90">
-        <v>-81.76364467199997</v>
+        <v>-84.06839631600005</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3896541210459165</v>
+        <v>0.4209135865955453</v>
       </c>
       <c r="T90">
-        <v>7.941203719305232</v>
+        <v>8.663131330151163</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02815325033780517</v>
+        <v>0.02783692168232421</v>
       </c>
       <c r="W90">
-        <v>0.2291614635703456</v>
+        <v>0.229236053867308</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1279693197172962</v>
+        <v>0.1265314621923828</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2503205824674141</v>
+        <v>0.2522205824674141</v>
       </c>
       <c r="C91">
-        <v>-881.9093639972004</v>
+        <v>-896.4474037189818</v>
       </c>
       <c r="D91">
-        <v>218.0496360027995</v>
+        <v>216.0425962810181</v>
       </c>
       <c r="E91">
-        <v>579.859</v>
+        <v>592.39</v>
       </c>
       <c r="F91">
-        <v>1115.259</v>
+        <v>1127.79</v>
       </c>
       <c r="G91">
         <v>15.3</v>
@@ -8755,37 +8755,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M91">
-        <v>262.9780722</v>
+        <v>265.932882</v>
       </c>
       <c r="N91">
-        <v>-229.7030722</v>
+        <v>-232.657882</v>
       </c>
       <c r="O91">
-        <v>-50.53467588400001</v>
+        <v>-51.18473404</v>
       </c>
       <c r="P91">
-        <v>-179.168396316</v>
+        <v>-181.47314796</v>
       </c>
       <c r="Q91">
-        <v>-84.06839631600005</v>
+        <v>-86.37314796000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4209135865955453</v>
+        <v>0.4584249452550999</v>
       </c>
       <c r="T91">
-        <v>8.663131330151163</v>
+        <v>9.52944446316628</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02783692168232421</v>
+        <v>0.0275276225525206</v>
       </c>
       <c r="W91">
-        <v>0.229236053867308</v>
+        <v>0.2293089866021157</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1265314621923828</v>
+        <v>0.1251255570569119</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2522205824674141</v>
+        <v>0.2541205824674141</v>
       </c>
       <c r="C92">
-        <v>-896.4474037189818</v>
+        <v>-910.9488327955139</v>
       </c>
       <c r="D92">
-        <v>216.0425962810181</v>
+        <v>214.072167204486</v>
       </c>
       <c r="E92">
-        <v>592.39</v>
+        <v>604.9209999999999</v>
       </c>
       <c r="F92">
-        <v>1127.79</v>
+        <v>1140.321</v>
       </c>
       <c r="G92">
         <v>15.3</v>
@@ -8837,37 +8837,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M92">
-        <v>265.932882</v>
+        <v>268.8876918</v>
       </c>
       <c r="N92">
-        <v>-232.657882</v>
+        <v>-235.6126918</v>
       </c>
       <c r="O92">
-        <v>-51.18473404</v>
+        <v>-51.834792196</v>
       </c>
       <c r="P92">
-        <v>-181.47314796</v>
+        <v>-183.777899604</v>
       </c>
       <c r="Q92">
-        <v>-86.37314796000001</v>
+        <v>-88.67789960399998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4584249452550999</v>
+        <v>0.5042721613945554</v>
       </c>
       <c r="T92">
-        <v>9.52944446316628</v>
+        <v>10.58827162574031</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0275276225525206</v>
+        <v>0.02722512120578961</v>
       </c>
       <c r="W92">
-        <v>0.2293089866021157</v>
+        <v>0.2293803164196748</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1251255570569119</v>
+        <v>0.1237505509354073</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2541205824674141</v>
+        <v>0.256020582467414</v>
       </c>
       <c r="C93">
-        <v>-910.9488327955139</v>
+        <v>-925.4146439016127</v>
       </c>
       <c r="D93">
-        <v>214.072167204486</v>
+        <v>212.1373560983871</v>
       </c>
       <c r="E93">
-        <v>604.9209999999999</v>
+        <v>617.4519999999999</v>
       </c>
       <c r="F93">
-        <v>1140.321</v>
+        <v>1152.852</v>
       </c>
       <c r="G93">
         <v>15.3</v>
@@ -8919,37 +8919,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M93">
-        <v>268.8876918</v>
+        <v>271.8425016</v>
       </c>
       <c r="N93">
-        <v>-235.6126918</v>
+        <v>-238.5675016</v>
       </c>
       <c r="O93">
-        <v>-51.834792196</v>
+        <v>-52.484850352</v>
       </c>
       <c r="P93">
-        <v>-183.777899604</v>
+        <v>-186.082651248</v>
       </c>
       <c r="Q93">
-        <v>-88.67789960399998</v>
+        <v>-90.982651248</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5042721613945554</v>
+        <v>0.5615811815688749</v>
       </c>
       <c r="T93">
-        <v>10.58827162574031</v>
+        <v>11.91180557895786</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02722512120578961</v>
+        <v>0.0269291959752919</v>
       </c>
       <c r="W93">
-        <v>0.2293803164196748</v>
+        <v>0.2294500955890262</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1237505509354073</v>
+        <v>0.1224054362513268</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.256020582467414</v>
+        <v>0.2579205824674141</v>
       </c>
       <c r="C94">
-        <v>-925.4146439016127</v>
+        <v>-939.8457941458678</v>
       </c>
       <c r="D94">
-        <v>212.1373560983871</v>
+        <v>210.2372058541323</v>
       </c>
       <c r="E94">
-        <v>617.4519999999999</v>
+        <v>629.9830000000001</v>
       </c>
       <c r="F94">
-        <v>1152.852</v>
+        <v>1165.383</v>
       </c>
       <c r="G94">
         <v>15.3</v>
@@ -9001,37 +9001,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M94">
-        <v>271.8425016</v>
+        <v>274.7973114</v>
       </c>
       <c r="N94">
-        <v>-238.5675016</v>
+        <v>-241.5223114</v>
       </c>
       <c r="O94">
-        <v>-52.484850352</v>
+        <v>-53.134908508</v>
       </c>
       <c r="P94">
-        <v>-186.082651248</v>
+        <v>-188.387402892</v>
       </c>
       <c r="Q94">
-        <v>-90.982651248</v>
+        <v>-93.28740289200002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5615811815688749</v>
+        <v>0.6352642075072856</v>
       </c>
       <c r="T94">
-        <v>11.91180557895786</v>
+        <v>13.61349209023755</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0269291959752919</v>
+        <v>0.02663963472824575</v>
       </c>
       <c r="W94">
-        <v>0.2294500955890262</v>
+        <v>0.2295183741310797</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1224054362513268</v>
+        <v>0.1210892487647534</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2579205824674141</v>
+        <v>0.2598205824674141</v>
       </c>
       <c r="C95">
-        <v>-939.8457941458678</v>
+        <v>-954.2432066493645</v>
       </c>
       <c r="D95">
-        <v>210.2372058541323</v>
+        <v>208.3707933506354</v>
       </c>
       <c r="E95">
-        <v>629.9830000000001</v>
+        <v>642.514</v>
       </c>
       <c r="F95">
-        <v>1165.383</v>
+        <v>1177.914</v>
       </c>
       <c r="G95">
         <v>15.3</v>
@@ -9083,37 +9083,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M95">
-        <v>274.7973114</v>
+        <v>277.7521212</v>
       </c>
       <c r="N95">
-        <v>-241.5223114</v>
+        <v>-244.4771212</v>
       </c>
       <c r="O95">
-        <v>-53.134908508</v>
+        <v>-53.78496666400001</v>
       </c>
       <c r="P95">
-        <v>-188.387402892</v>
+        <v>-190.692154536</v>
       </c>
       <c r="Q95">
-        <v>-93.28740289200002</v>
+        <v>-95.59215453600004</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6352642075072856</v>
+        <v>0.7335082420918335</v>
       </c>
       <c r="T95">
-        <v>13.61349209023755</v>
+        <v>15.88240743861048</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02663963472824575</v>
+        <v>0.02635623435879632</v>
       </c>
       <c r="W95">
-        <v>0.2295183741310797</v>
+        <v>0.2295851999381958</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1210892487647534</v>
+        <v>0.119801065267256</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2598205824674141</v>
+        <v>0.2617205824674141</v>
       </c>
       <c r="C96">
-        <v>-954.2432066493645</v>
+        <v>-968.6077720410564</v>
       </c>
       <c r="D96">
-        <v>208.3707933506354</v>
+        <v>206.5372279589436</v>
       </c>
       <c r="E96">
-        <v>642.514</v>
+        <v>655.045</v>
       </c>
       <c r="F96">
-        <v>1177.914</v>
+        <v>1190.445</v>
       </c>
       <c r="G96">
         <v>15.3</v>
@@ -9165,37 +9165,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M96">
-        <v>277.7521212</v>
+        <v>280.706931</v>
       </c>
       <c r="N96">
-        <v>-244.4771212</v>
+        <v>-247.431931</v>
       </c>
       <c r="O96">
-        <v>-53.78496666400001</v>
+        <v>-54.43502482</v>
       </c>
       <c r="P96">
-        <v>-190.692154536</v>
+        <v>-192.99690618</v>
       </c>
       <c r="Q96">
-        <v>-95.59215453600004</v>
+        <v>-97.89690618</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7335082420918335</v>
+        <v>0.8710498905102008</v>
       </c>
       <c r="T96">
-        <v>15.88240743861048</v>
+        <v>19.05888892633259</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02635623435879632</v>
+        <v>0.02607880031291426</v>
       </c>
       <c r="W96">
-        <v>0.2295851999381958</v>
+        <v>0.2296506188862149</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.119801065267256</v>
+        <v>0.1185400014223376</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2617205824674141</v>
+        <v>0.263620582467414</v>
       </c>
       <c r="C97">
-        <v>-968.6077720410564</v>
+        <v>-982.9403498748716</v>
       </c>
       <c r="D97">
-        <v>206.5372279589436</v>
+        <v>204.7356501251285</v>
       </c>
       <c r="E97">
-        <v>655.045</v>
+        <v>667.5760000000001</v>
       </c>
       <c r="F97">
-        <v>1190.445</v>
+        <v>1202.976</v>
       </c>
       <c r="G97">
         <v>15.3</v>
@@ -9247,37 +9247,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M97">
-        <v>280.706931</v>
+        <v>283.6617408</v>
       </c>
       <c r="N97">
-        <v>-247.431931</v>
+        <v>-250.3867408</v>
       </c>
       <c r="O97">
-        <v>-54.43502482</v>
+        <v>-55.085082976</v>
       </c>
       <c r="P97">
-        <v>-192.99690618</v>
+        <v>-195.301657824</v>
       </c>
       <c r="Q97">
-        <v>-97.89690618</v>
+        <v>-100.201657824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8710498905102008</v>
+        <v>1.077362363137751</v>
       </c>
       <c r="T97">
-        <v>19.05888892633259</v>
+        <v>23.82361115791574</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02607880031291426</v>
+        <v>0.02580714614298807</v>
       </c>
       <c r="W97">
-        <v>0.2296506188862149</v>
+        <v>0.2297146749394834</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1185400014223376</v>
+        <v>0.1173052097408549</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.263620582467414</v>
+        <v>0.2655205824674141</v>
       </c>
       <c r="C98">
-        <v>-982.9403498748713</v>
+        <v>-997.2417699732954</v>
       </c>
       <c r="D98">
-        <v>204.7356501251285</v>
+        <v>202.9652300267044</v>
       </c>
       <c r="E98">
-        <v>667.5759999999999</v>
+        <v>680.1069999999999</v>
       </c>
       <c r="F98">
-        <v>1202.976</v>
+        <v>1215.507</v>
       </c>
       <c r="G98">
         <v>15.3</v>
@@ -9329,37 +9329,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M98">
-        <v>283.6617408</v>
+        <v>286.6165506</v>
       </c>
       <c r="N98">
-        <v>-250.3867408</v>
+        <v>-253.3415506</v>
       </c>
       <c r="O98">
-        <v>-55.08508297599999</v>
+        <v>-55.735141132</v>
       </c>
       <c r="P98">
-        <v>-195.301657824</v>
+        <v>-197.606409468</v>
       </c>
       <c r="Q98">
-        <v>-100.201657824</v>
+        <v>-102.506409468</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.077362363137748</v>
+        <v>1.421216484183665</v>
       </c>
       <c r="T98">
-        <v>23.82361115791567</v>
+        <v>31.7648148772209</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02580714614298807</v>
+        <v>0.02554109308996757</v>
       </c>
       <c r="W98">
-        <v>0.2297146749394834</v>
+        <v>0.2297774102493857</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1173052097408549</v>
+        <v>0.1160958776816708</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2655205824674141</v>
+        <v>0.2674205824674141</v>
       </c>
       <c r="C99">
-        <v>-997.2417699732954</v>
+        <v>-1011.512833701841</v>
       </c>
       <c r="D99">
-        <v>202.9652300267044</v>
+        <v>201.2251662981587</v>
       </c>
       <c r="E99">
-        <v>680.1069999999999</v>
+        <v>692.6379999999998</v>
       </c>
       <c r="F99">
-        <v>1215.507</v>
+        <v>1228.038</v>
       </c>
       <c r="G99">
         <v>15.3</v>
@@ -9411,37 +9411,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M99">
-        <v>286.6165506</v>
+        <v>289.5713603999999</v>
       </c>
       <c r="N99">
-        <v>-253.3415506</v>
+        <v>-256.2963603999999</v>
       </c>
       <c r="O99">
-        <v>-55.735141132</v>
+        <v>-56.38519928799998</v>
       </c>
       <c r="P99">
-        <v>-197.606409468</v>
+        <v>-199.9111611119999</v>
       </c>
       <c r="Q99">
-        <v>-102.506409468</v>
+        <v>-104.811161112</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.421216484183665</v>
+        <v>2.108924726275497</v>
       </c>
       <c r="T99">
-        <v>31.7648148772209</v>
+        <v>47.64722231583135</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02554109308996757</v>
+        <v>0.02528046969109036</v>
       </c>
       <c r="W99">
-        <v>0.2297774102493857</v>
+        <v>0.2298388652468409</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1160958776816708</v>
+        <v>0.1149112258685926</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2674205824674141</v>
+        <v>0.2693205824674141</v>
       </c>
       <c r="C100">
-        <v>-1011.512833701841</v>
+        <v>-1025.754315178518</v>
       </c>
       <c r="D100">
-        <v>201.2251662981587</v>
+        <v>199.5146848214819</v>
       </c>
       <c r="E100">
-        <v>692.6379999999998</v>
+        <v>705.169</v>
       </c>
       <c r="F100">
-        <v>1228.038</v>
+        <v>1240.569</v>
       </c>
       <c r="G100">
         <v>15.3</v>
@@ -9493,37 +9493,37 @@
         <v>33.27500000000001</v>
       </c>
       <c r="M100">
-        <v>289.5713603999999</v>
+        <v>292.5261702</v>
       </c>
       <c r="N100">
-        <v>-256.2963603999999</v>
+        <v>-259.2511702</v>
       </c>
       <c r="O100">
-        <v>-56.38519928799998</v>
+        <v>-57.03525744400001</v>
       </c>
       <c r="P100">
-        <v>-199.9111611119999</v>
+        <v>-202.215912756</v>
       </c>
       <c r="Q100">
-        <v>-104.811161112</v>
+        <v>-107.115912756</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.108924726275497</v>
+        <v>4.172049452550993</v>
       </c>
       <c r="T100">
-        <v>47.64722231583135</v>
+        <v>95.29444463166269</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02528046969109036</v>
+        <v>0.02502511141138237</v>
       </c>
       <c r="W100">
-        <v>0.2298388652468409</v>
+        <v>0.229899078729196</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1149112258685926</v>
+        <v>0.1137505064153743</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2693205824674141</v>
-      </c>
-      <c r="C101">
-        <v>-1025.754315178518</v>
-      </c>
-      <c r="D101">
-        <v>199.5146848214819</v>
-      </c>
-      <c r="E101">
-        <v>705.169</v>
-      </c>
-      <c r="F101">
-        <v>1240.569</v>
-      </c>
-      <c r="G101">
-        <v>15.3</v>
-      </c>
-      <c r="H101">
-        <v>717.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>128.375</v>
-      </c>
-      <c r="K101">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="L101">
-        <v>33.27500000000001</v>
-      </c>
-      <c r="M101">
-        <v>292.5261702</v>
-      </c>
-      <c r="N101">
-        <v>-259.2511702</v>
-      </c>
-      <c r="O101">
-        <v>-57.03525744400001</v>
-      </c>
-      <c r="P101">
-        <v>-202.215912756</v>
-      </c>
-      <c r="Q101">
-        <v>-107.115912756</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.172049452550993</v>
-      </c>
-      <c r="T101">
-        <v>95.29444463166269</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02502511141138237</v>
-      </c>
-      <c r="W101">
-        <v>0.229899078729196</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1137505064153743</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
